--- a/data_raw/smelt/SFBS_2026.xlsx
+++ b/data_raw/smelt/SFBS_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/lmccormick_usbr_gov/Documents/Documents/Research/R/samt_smt_assessments/data_raw/smelt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BA8C4A5-8E3C-4995-9D3D-F7C3C7E2E2F8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B39F03-9EBE-4F56-B6F5-4D4EC5D7AE55}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="23040" windowHeight="12120" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
+    <workbookView xWindow="12192" yWindow="-14112" windowWidth="22332" windowHeight="12300" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="46">
   <si>
     <t>Year</t>
   </si>
@@ -142,6 +142,39 @@
   <si>
     <t>1204.2199848890305</t>
   </si>
+  <si>
+    <t>2026-02-11T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-02-12T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2154.9200226664543</t>
+  </si>
+  <si>
+    <t>2026-02-10T00:00:00Z</t>
+  </si>
+  <si>
+    <t>1014.0799773335457</t>
+  </si>
+  <si>
+    <t>1457.7400264441967</t>
+  </si>
+  <si>
+    <t>2026-02-20T00:00:00Z</t>
+  </si>
+  <si>
+    <t>950.7000377774239</t>
+  </si>
+  <si>
+    <t>2026-02-18T00:00:00Z</t>
+  </si>
+  <si>
+    <t>697.1799962222576</t>
+  </si>
 </sst>
 </file>
 
@@ -194,6 +227,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84FFA20-E1FB-43B3-8FA5-E079A449C1F1}">
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -4080,6 +4117,5008 @@
         <v>4136.55</v>
       </c>
     </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>2026</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88">
+        <v>427</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>110</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>15</v>
+      </c>
+      <c r="L88" t="s">
+        <v>15</v>
+      </c>
+      <c r="M88">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>2026</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89">
+        <v>432</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>110</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+      <c r="L89">
+        <v>633.80000944435596</v>
+      </c>
+      <c r="M89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>2026</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90">
+        <v>140</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>108</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>15</v>
+      </c>
+      <c r="L90" t="s">
+        <v>15</v>
+      </c>
+      <c r="M90">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>2026</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91">
+        <v>427</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>106</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" t="s">
+        <v>15</v>
+      </c>
+      <c r="L91" t="s">
+        <v>15</v>
+      </c>
+      <c r="M91">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>2026</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92" t="s">
+        <v>37</v>
+      </c>
+      <c r="D92">
+        <v>325</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>105</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" t="s">
+        <v>15</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M92" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>2026</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93">
+        <v>325</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>104</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>2026</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+      <c r="C94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94">
+        <v>427</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>103</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" t="s">
+        <v>15</v>
+      </c>
+      <c r="M94">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>2026</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95">
+        <v>429</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>103</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" t="s">
+        <v>15</v>
+      </c>
+      <c r="M95">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>2026</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>35</v>
+      </c>
+      <c r="D96">
+        <v>433</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>99</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+      <c r="L96" t="s">
+        <v>15</v>
+      </c>
+      <c r="M96">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>2026</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97" t="s">
+        <v>35</v>
+      </c>
+      <c r="D97">
+        <v>428</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>98</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
+        <v>15</v>
+      </c>
+      <c r="L97" t="s">
+        <v>15</v>
+      </c>
+      <c r="M97">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>2026</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98">
+        <v>432</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>97</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" t="s">
+        <v>15</v>
+      </c>
+      <c r="L98" t="s">
+        <v>15</v>
+      </c>
+      <c r="M98">
+        <v>5249.1750000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>2026</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99">
+        <v>101</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>93</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" t="s">
+        <v>15</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M99" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>2026</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100" t="s">
+        <v>36</v>
+      </c>
+      <c r="D100">
+        <v>140</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>92</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>2026</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101">
+        <v>140</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>91</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+      <c r="L101" t="s">
+        <v>15</v>
+      </c>
+      <c r="M101">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>2026</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102">
+        <v>101</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>90</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102" t="s">
+        <v>15</v>
+      </c>
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>2026</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>35</v>
+      </c>
+      <c r="D103">
+        <v>429</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>90</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+      <c r="L103" t="s">
+        <v>15</v>
+      </c>
+      <c r="M103">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>2026</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>35</v>
+      </c>
+      <c r="D104">
+        <v>429</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>89</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104" t="s">
+        <v>15</v>
+      </c>
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+      <c r="L104" t="s">
+        <v>15</v>
+      </c>
+      <c r="M104">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>2026</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105">
+        <v>140</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>88</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105" t="s">
+        <v>15</v>
+      </c>
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+      <c r="L105" t="s">
+        <v>15</v>
+      </c>
+      <c r="M105">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>2026</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106" t="s">
+        <v>37</v>
+      </c>
+      <c r="D106">
+        <v>345</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>88</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106" t="s">
+        <v>15</v>
+      </c>
+      <c r="K106" t="s">
+        <v>15</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M106" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>2026</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>35</v>
+      </c>
+      <c r="D107">
+        <v>429</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>88</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107" t="s">
+        <v>15</v>
+      </c>
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+      <c r="L107" t="s">
+        <v>15</v>
+      </c>
+      <c r="M107">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>2026</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108">
+        <v>140</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>87</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108" t="s">
+        <v>15</v>
+      </c>
+      <c r="K108" t="s">
+        <v>15</v>
+      </c>
+      <c r="L108" t="s">
+        <v>15</v>
+      </c>
+      <c r="M108">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>2026</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109">
+        <v>325</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>87</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109" t="s">
+        <v>15</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+      <c r="L109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>2026</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>35</v>
+      </c>
+      <c r="D110">
+        <v>433</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>87</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+      <c r="L110" t="s">
+        <v>15</v>
+      </c>
+      <c r="M110">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>2026</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111">
+        <v>432</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>86</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
+        <v>15</v>
+      </c>
+      <c r="K111" t="s">
+        <v>15</v>
+      </c>
+      <c r="L111" t="s">
+        <v>15</v>
+      </c>
+      <c r="M111">
+        <v>5249.1750000000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>2026</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112">
+        <v>325</v>
+      </c>
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>85</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>15</v>
+      </c>
+      <c r="K112" t="s">
+        <v>15</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>2026</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>36</v>
+      </c>
+      <c r="D113">
+        <v>140</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>84</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>15</v>
+      </c>
+      <c r="K113" t="s">
+        <v>15</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>2026</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114">
+        <v>321</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>84</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>15</v>
+      </c>
+      <c r="K114" t="s">
+        <v>15</v>
+      </c>
+      <c r="L114" t="s">
+        <v>15</v>
+      </c>
+      <c r="M114">
+        <v>7250.1750000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>2026</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>35</v>
+      </c>
+      <c r="D115">
+        <v>427</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>84</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115" t="s">
+        <v>15</v>
+      </c>
+      <c r="K115" t="s">
+        <v>15</v>
+      </c>
+      <c r="L115" t="s">
+        <v>15</v>
+      </c>
+      <c r="M115">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>2026</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116">
+        <v>429</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>84</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+      <c r="J116" t="s">
+        <v>15</v>
+      </c>
+      <c r="K116" t="s">
+        <v>15</v>
+      </c>
+      <c r="L116" t="s">
+        <v>15</v>
+      </c>
+      <c r="M116">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>2026</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>36</v>
+      </c>
+      <c r="D117">
+        <v>140</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>83</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
+        <v>15</v>
+      </c>
+      <c r="K117" t="s">
+        <v>15</v>
+      </c>
+      <c r="L117" t="s">
+        <v>15</v>
+      </c>
+      <c r="M117">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>2026</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118">
+        <v>325</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>83</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118" t="s">
+        <v>15</v>
+      </c>
+      <c r="K118" t="s">
+        <v>15</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M118" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>2026</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>35</v>
+      </c>
+      <c r="D119">
+        <v>427</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>83</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
+        <v>15</v>
+      </c>
+      <c r="K119" t="s">
+        <v>15</v>
+      </c>
+      <c r="L119" t="s">
+        <v>15</v>
+      </c>
+      <c r="M119">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>2026</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>35</v>
+      </c>
+      <c r="D120">
+        <v>429</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>83</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120" t="s">
+        <v>15</v>
+      </c>
+      <c r="K120" t="s">
+        <v>15</v>
+      </c>
+      <c r="L120" t="s">
+        <v>15</v>
+      </c>
+      <c r="M120">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>2026</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>35</v>
+      </c>
+      <c r="D121">
+        <v>432</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>83</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
+        <v>15</v>
+      </c>
+      <c r="K121" t="s">
+        <v>15</v>
+      </c>
+      <c r="L121" t="s">
+        <v>15</v>
+      </c>
+      <c r="M121">
+        <v>5249.1750000000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122">
+        <v>433</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>14</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>83</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122" t="s">
+        <v>15</v>
+      </c>
+      <c r="K122" t="s">
+        <v>15</v>
+      </c>
+      <c r="L122" t="s">
+        <v>15</v>
+      </c>
+      <c r="M122">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>2026</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>39</v>
+      </c>
+      <c r="D123">
+        <v>736</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>83</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>15</v>
+      </c>
+      <c r="K123" t="s">
+        <v>15</v>
+      </c>
+      <c r="L123" t="s">
+        <v>15</v>
+      </c>
+      <c r="M123">
+        <v>6797.65</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>2026</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124">
+        <v>325</v>
+      </c>
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>82</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124" t="s">
+        <v>15</v>
+      </c>
+      <c r="K124" t="s">
+        <v>15</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M124" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>2026</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>35</v>
+      </c>
+      <c r="D125">
+        <v>427</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>82</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125" t="s">
+        <v>15</v>
+      </c>
+      <c r="K125" t="s">
+        <v>15</v>
+      </c>
+      <c r="L125" t="s">
+        <v>15</v>
+      </c>
+      <c r="M125">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>2026</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>35</v>
+      </c>
+      <c r="D126">
+        <v>429</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>82</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126" t="s">
+        <v>15</v>
+      </c>
+      <c r="K126" t="s">
+        <v>15</v>
+      </c>
+      <c r="L126" t="s">
+        <v>15</v>
+      </c>
+      <c r="M126">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>2026</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>35</v>
+      </c>
+      <c r="D127">
+        <v>429</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>82</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127" t="s">
+        <v>15</v>
+      </c>
+      <c r="K127" t="s">
+        <v>15</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M127" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>2026</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>36</v>
+      </c>
+      <c r="D128">
+        <v>101</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>81</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128" t="s">
+        <v>15</v>
+      </c>
+      <c r="K128" t="s">
+        <v>15</v>
+      </c>
+      <c r="L128" t="s">
+        <v>15</v>
+      </c>
+      <c r="M128">
+        <v>6225.5249999999996</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>2026</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>36</v>
+      </c>
+      <c r="D129">
+        <v>140</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>81</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129" t="s">
+        <v>15</v>
+      </c>
+      <c r="K129" t="s">
+        <v>15</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>2026</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130" t="s">
+        <v>36</v>
+      </c>
+      <c r="D130">
+        <v>140</v>
+      </c>
+      <c r="E130">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>81</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130" t="s">
+        <v>15</v>
+      </c>
+      <c r="K130" t="s">
+        <v>15</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>2026</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>36</v>
+      </c>
+      <c r="D131">
+        <v>140</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>81</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131" t="s">
+        <v>15</v>
+      </c>
+      <c r="K131" t="s">
+        <v>15</v>
+      </c>
+      <c r="L131" t="s">
+        <v>15</v>
+      </c>
+      <c r="M131">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>2026</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>35</v>
+      </c>
+      <c r="D132">
+        <v>427</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>81</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132" t="s">
+        <v>15</v>
+      </c>
+      <c r="K132" t="s">
+        <v>15</v>
+      </c>
+      <c r="L132" t="s">
+        <v>15</v>
+      </c>
+      <c r="M132">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>2026</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="C133" t="s">
+        <v>35</v>
+      </c>
+      <c r="D133">
+        <v>429</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>81</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
+        <v>15</v>
+      </c>
+      <c r="K133" t="s">
+        <v>15</v>
+      </c>
+      <c r="L133" t="s">
+        <v>15</v>
+      </c>
+      <c r="M133">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>2026</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>36</v>
+      </c>
+      <c r="D134">
+        <v>101</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>80</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
+        <v>15</v>
+      </c>
+      <c r="K134" t="s">
+        <v>15</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M134" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>2026</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>36</v>
+      </c>
+      <c r="D135">
+        <v>101</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>79</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135" t="s">
+        <v>15</v>
+      </c>
+      <c r="K135" t="s">
+        <v>15</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M135" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>2026</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>36</v>
+      </c>
+      <c r="D136">
+        <v>140</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>79</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136" t="s">
+        <v>15</v>
+      </c>
+      <c r="K136" t="s">
+        <v>15</v>
+      </c>
+      <c r="L136" t="s">
+        <v>15</v>
+      </c>
+      <c r="M136">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>2026</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>37</v>
+      </c>
+      <c r="D137">
+        <v>325</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>79</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137" t="s">
+        <v>15</v>
+      </c>
+      <c r="K137" t="s">
+        <v>15</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M137" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>2026</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>35</v>
+      </c>
+      <c r="D138">
+        <v>428</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>79</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138" t="s">
+        <v>15</v>
+      </c>
+      <c r="K138" t="s">
+        <v>15</v>
+      </c>
+      <c r="L138" t="s">
+        <v>15</v>
+      </c>
+      <c r="M138">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>2026</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>36</v>
+      </c>
+      <c r="D139">
+        <v>101</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>78</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139" t="s">
+        <v>15</v>
+      </c>
+      <c r="K139" t="s">
+        <v>15</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M139" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>2026</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>37</v>
+      </c>
+      <c r="D140">
+        <v>325</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>78</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140" t="s">
+        <v>15</v>
+      </c>
+      <c r="K140" t="s">
+        <v>15</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M140" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>2026</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>35</v>
+      </c>
+      <c r="D141">
+        <v>427</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>78</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141" t="s">
+        <v>15</v>
+      </c>
+      <c r="K141" t="s">
+        <v>15</v>
+      </c>
+      <c r="L141" t="s">
+        <v>15</v>
+      </c>
+      <c r="M141">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>2026</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142">
+        <v>428</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>78</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142" t="s">
+        <v>15</v>
+      </c>
+      <c r="K142" t="s">
+        <v>15</v>
+      </c>
+      <c r="L142" t="s">
+        <v>15</v>
+      </c>
+      <c r="M142">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>2026</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>35</v>
+      </c>
+      <c r="D143">
+        <v>429</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>78</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143" t="s">
+        <v>15</v>
+      </c>
+      <c r="K143" t="s">
+        <v>15</v>
+      </c>
+      <c r="L143" t="s">
+        <v>15</v>
+      </c>
+      <c r="M143">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>2026</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>35</v>
+      </c>
+      <c r="D144">
+        <v>429</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>78</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144" t="s">
+        <v>15</v>
+      </c>
+      <c r="K144" t="s">
+        <v>15</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>2026</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>35</v>
+      </c>
+      <c r="D145">
+        <v>432</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>78</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="J145" t="s">
+        <v>15</v>
+      </c>
+      <c r="K145" t="s">
+        <v>15</v>
+      </c>
+      <c r="L145" t="s">
+        <v>15</v>
+      </c>
+      <c r="M145">
+        <v>5249.1750000000002</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>2026</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>35</v>
+      </c>
+      <c r="D146">
+        <v>433</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>78</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146" t="s">
+        <v>15</v>
+      </c>
+      <c r="K146" t="s">
+        <v>15</v>
+      </c>
+      <c r="L146" t="s">
+        <v>15</v>
+      </c>
+      <c r="M146">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>2026</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>35</v>
+      </c>
+      <c r="D147">
+        <v>535</v>
+      </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
+      <c r="F147" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>78</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147" t="s">
+        <v>15</v>
+      </c>
+      <c r="K147" t="s">
+        <v>15</v>
+      </c>
+      <c r="L147" t="s">
+        <v>15</v>
+      </c>
+      <c r="M147">
+        <v>6956.6374999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>2026</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>37</v>
+      </c>
+      <c r="D148">
+        <v>321</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>77</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148" t="s">
+        <v>15</v>
+      </c>
+      <c r="K148" t="s">
+        <v>15</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M148" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>2026</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>37</v>
+      </c>
+      <c r="D149">
+        <v>325</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>77</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149" t="s">
+        <v>15</v>
+      </c>
+      <c r="K149" t="s">
+        <v>15</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>2026</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>37</v>
+      </c>
+      <c r="D150">
+        <v>346</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>77</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150" t="s">
+        <v>15</v>
+      </c>
+      <c r="K150" t="s">
+        <v>15</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M150" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>2026</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>35</v>
+      </c>
+      <c r="D151">
+        <v>427</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>77</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151" t="s">
+        <v>15</v>
+      </c>
+      <c r="K151" t="s">
+        <v>15</v>
+      </c>
+      <c r="L151" t="s">
+        <v>15</v>
+      </c>
+      <c r="M151">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>2026</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>35</v>
+      </c>
+      <c r="D152">
+        <v>428</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>77</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152" t="s">
+        <v>15</v>
+      </c>
+      <c r="K152" t="s">
+        <v>15</v>
+      </c>
+      <c r="L152" t="s">
+        <v>15</v>
+      </c>
+      <c r="M152">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>2026</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>35</v>
+      </c>
+      <c r="D153">
+        <v>433</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>77</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153" t="s">
+        <v>15</v>
+      </c>
+      <c r="K153" t="s">
+        <v>15</v>
+      </c>
+      <c r="L153" t="s">
+        <v>15</v>
+      </c>
+      <c r="M153">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>2026</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>36</v>
+      </c>
+      <c r="D154">
+        <v>140</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>76</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154" t="s">
+        <v>15</v>
+      </c>
+      <c r="K154" t="s">
+        <v>15</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M154" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>2026</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>37</v>
+      </c>
+      <c r="D155">
+        <v>321</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>76</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155" t="s">
+        <v>15</v>
+      </c>
+      <c r="K155" t="s">
+        <v>15</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M155" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>2026</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>37</v>
+      </c>
+      <c r="D156">
+        <v>325</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>76</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156" t="s">
+        <v>15</v>
+      </c>
+      <c r="K156" t="s">
+        <v>15</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M156" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>2026</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157" t="s">
+        <v>35</v>
+      </c>
+      <c r="D157">
+        <v>427</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="F157" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>76</v>
+      </c>
+      <c r="I157">
+        <v>3</v>
+      </c>
+      <c r="J157" t="s">
+        <v>15</v>
+      </c>
+      <c r="K157" t="s">
+        <v>15</v>
+      </c>
+      <c r="L157" t="s">
+        <v>15</v>
+      </c>
+      <c r="M157">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>2026</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158" t="s">
+        <v>35</v>
+      </c>
+      <c r="D158">
+        <v>428</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>76</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158" t="s">
+        <v>15</v>
+      </c>
+      <c r="K158" t="s">
+        <v>15</v>
+      </c>
+      <c r="L158" t="s">
+        <v>15</v>
+      </c>
+      <c r="M158">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>2026</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>37</v>
+      </c>
+      <c r="D159">
+        <v>325</v>
+      </c>
+      <c r="E159">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>75</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159" t="s">
+        <v>15</v>
+      </c>
+      <c r="K159" t="s">
+        <v>15</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M159" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>2026</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
+        <v>35</v>
+      </c>
+      <c r="D160">
+        <v>427</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>75</v>
+      </c>
+      <c r="I160">
+        <v>3</v>
+      </c>
+      <c r="J160" t="s">
+        <v>15</v>
+      </c>
+      <c r="K160" t="s">
+        <v>15</v>
+      </c>
+      <c r="L160" t="s">
+        <v>15</v>
+      </c>
+      <c r="M160">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>2026</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
+        <v>35</v>
+      </c>
+      <c r="D161">
+        <v>428</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161" t="s">
+        <v>14</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>75</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161" t="s">
+        <v>15</v>
+      </c>
+      <c r="K161" t="s">
+        <v>15</v>
+      </c>
+      <c r="L161" t="s">
+        <v>15</v>
+      </c>
+      <c r="M161">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>2026</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162" t="s">
+        <v>35</v>
+      </c>
+      <c r="D162">
+        <v>429</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>75</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162" t="s">
+        <v>15</v>
+      </c>
+      <c r="K162" t="s">
+        <v>15</v>
+      </c>
+      <c r="L162" t="s">
+        <v>15</v>
+      </c>
+      <c r="M162">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>2026</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>36</v>
+      </c>
+      <c r="D163">
+        <v>101</v>
+      </c>
+      <c r="E163">
+        <v>2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>14</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>74</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163" t="s">
+        <v>15</v>
+      </c>
+      <c r="K163" t="s">
+        <v>15</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M163" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>2026</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>35</v>
+      </c>
+      <c r="D164">
+        <v>429</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>74</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164" t="s">
+        <v>15</v>
+      </c>
+      <c r="K164" t="s">
+        <v>15</v>
+      </c>
+      <c r="L164" t="s">
+        <v>15</v>
+      </c>
+      <c r="M164">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>2026</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
+        <v>39</v>
+      </c>
+      <c r="D165">
+        <v>761</v>
+      </c>
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>14</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>74</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165" t="s">
+        <v>15</v>
+      </c>
+      <c r="K165" t="s">
+        <v>15</v>
+      </c>
+      <c r="L165" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M165" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>2026</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166" t="s">
+        <v>36</v>
+      </c>
+      <c r="D166">
+        <v>140</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>14</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>73</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166" t="s">
+        <v>15</v>
+      </c>
+      <c r="K166" t="s">
+        <v>15</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M166" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>2026</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
+        <v>35</v>
+      </c>
+      <c r="D167">
+        <v>428</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167" t="s">
+        <v>14</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>73</v>
+      </c>
+      <c r="I167">
+        <v>2</v>
+      </c>
+      <c r="J167" t="s">
+        <v>15</v>
+      </c>
+      <c r="K167" t="s">
+        <v>15</v>
+      </c>
+      <c r="L167" t="s">
+        <v>15</v>
+      </c>
+      <c r="M167">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>2026</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+      <c r="C168" t="s">
+        <v>35</v>
+      </c>
+      <c r="D168">
+        <v>429</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168" t="s">
+        <v>14</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>73</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168" t="s">
+        <v>15</v>
+      </c>
+      <c r="K168" t="s">
+        <v>15</v>
+      </c>
+      <c r="L168" t="s">
+        <v>15</v>
+      </c>
+      <c r="M168">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>2026</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+      <c r="C169" t="s">
+        <v>35</v>
+      </c>
+      <c r="D169">
+        <v>534</v>
+      </c>
+      <c r="E169">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>73</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169" t="s">
+        <v>15</v>
+      </c>
+      <c r="K169" t="s">
+        <v>15</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M169" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>2026</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170" t="s">
+        <v>36</v>
+      </c>
+      <c r="D170">
+        <v>140</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>72</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170" t="s">
+        <v>15</v>
+      </c>
+      <c r="K170" t="s">
+        <v>15</v>
+      </c>
+      <c r="L170" t="s">
+        <v>15</v>
+      </c>
+      <c r="M170">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>2026</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="s">
+        <v>37</v>
+      </c>
+      <c r="D171">
+        <v>325</v>
+      </c>
+      <c r="E171">
+        <v>2</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>72</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171" t="s">
+        <v>15</v>
+      </c>
+      <c r="K171" t="s">
+        <v>15</v>
+      </c>
+      <c r="L171" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M171" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>2026</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="s">
+        <v>35</v>
+      </c>
+      <c r="D172">
+        <v>427</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>72</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172" t="s">
+        <v>15</v>
+      </c>
+      <c r="K172" t="s">
+        <v>15</v>
+      </c>
+      <c r="L172" t="s">
+        <v>15</v>
+      </c>
+      <c r="M172">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>2026</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173" t="s">
+        <v>35</v>
+      </c>
+      <c r="D173">
+        <v>433</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173" t="s">
+        <v>14</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>72</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173" t="s">
+        <v>15</v>
+      </c>
+      <c r="K173" t="s">
+        <v>15</v>
+      </c>
+      <c r="L173" t="s">
+        <v>15</v>
+      </c>
+      <c r="M173">
+        <v>7042.8874999999998</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>2026</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+      <c r="C174" t="s">
+        <v>42</v>
+      </c>
+      <c r="D174">
+        <v>108</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174" t="s">
+        <v>14</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>71</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174" t="s">
+        <v>15</v>
+      </c>
+      <c r="K174" t="s">
+        <v>15</v>
+      </c>
+      <c r="L174" t="s">
+        <v>15</v>
+      </c>
+      <c r="M174">
+        <v>6919.55</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>2026</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175" t="s">
+        <v>36</v>
+      </c>
+      <c r="D175">
+        <v>140</v>
+      </c>
+      <c r="E175">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>71</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175" t="s">
+        <v>15</v>
+      </c>
+      <c r="K175" t="s">
+        <v>15</v>
+      </c>
+      <c r="L175" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M175" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>2026</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+      <c r="C176" t="s">
+        <v>35</v>
+      </c>
+      <c r="D176">
+        <v>427</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176" t="s">
+        <v>14</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>71</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176" t="s">
+        <v>15</v>
+      </c>
+      <c r="K176" t="s">
+        <v>15</v>
+      </c>
+      <c r="L176" t="s">
+        <v>15</v>
+      </c>
+      <c r="M176">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>2026</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177" t="s">
+        <v>35</v>
+      </c>
+      <c r="D177">
+        <v>432</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177" t="s">
+        <v>14</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>71</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177" t="s">
+        <v>15</v>
+      </c>
+      <c r="K177" t="s">
+        <v>15</v>
+      </c>
+      <c r="L177" t="s">
+        <v>15</v>
+      </c>
+      <c r="M177">
+        <v>5249.1750000000002</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>2026</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178" t="s">
+        <v>36</v>
+      </c>
+      <c r="D178">
+        <v>101</v>
+      </c>
+      <c r="E178">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>70</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178" t="s">
+        <v>15</v>
+      </c>
+      <c r="K178" t="s">
+        <v>15</v>
+      </c>
+      <c r="L178" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M178" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>2026</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
+      </c>
+      <c r="C179" t="s">
+        <v>42</v>
+      </c>
+      <c r="D179">
+        <v>108</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>14</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>70</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179" t="s">
+        <v>15</v>
+      </c>
+      <c r="K179" t="s">
+        <v>15</v>
+      </c>
+      <c r="L179" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M179" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>2026</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="s">
+        <v>36</v>
+      </c>
+      <c r="D180">
+        <v>140</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180" t="s">
+        <v>14</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>70</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180" t="s">
+        <v>15</v>
+      </c>
+      <c r="K180" t="s">
+        <v>15</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M180" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>2026</v>
+      </c>
+      <c r="B181">
+        <v>2</v>
+      </c>
+      <c r="C181" t="s">
+        <v>37</v>
+      </c>
+      <c r="D181">
+        <v>321</v>
+      </c>
+      <c r="E181">
+        <v>2</v>
+      </c>
+      <c r="F181" t="s">
+        <v>14</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>70</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181" t="s">
+        <v>15</v>
+      </c>
+      <c r="K181" t="s">
+        <v>15</v>
+      </c>
+      <c r="L181" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>2026</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182" t="s">
+        <v>37</v>
+      </c>
+      <c r="D182">
+        <v>325</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182" t="s">
+        <v>14</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>70</v>
+      </c>
+      <c r="I182">
+        <v>2</v>
+      </c>
+      <c r="J182" t="s">
+        <v>15</v>
+      </c>
+      <c r="K182" t="s">
+        <v>15</v>
+      </c>
+      <c r="L182" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M182" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>2026</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
+        <v>35</v>
+      </c>
+      <c r="D183">
+        <v>427</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183" t="s">
+        <v>14</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>70</v>
+      </c>
+      <c r="I183">
+        <v>3</v>
+      </c>
+      <c r="J183" t="s">
+        <v>15</v>
+      </c>
+      <c r="K183" t="s">
+        <v>15</v>
+      </c>
+      <c r="L183" t="s">
+        <v>15</v>
+      </c>
+      <c r="M183">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>2026</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" t="s">
+        <v>36</v>
+      </c>
+      <c r="D184">
+        <v>140</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184" t="s">
+        <v>14</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>69</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184" t="s">
+        <v>15</v>
+      </c>
+      <c r="K184" t="s">
+        <v>15</v>
+      </c>
+      <c r="L184" t="s">
+        <v>15</v>
+      </c>
+      <c r="M184">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>2026</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" t="s">
+        <v>35</v>
+      </c>
+      <c r="D185">
+        <v>427</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>69</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185" t="s">
+        <v>15</v>
+      </c>
+      <c r="K185" t="s">
+        <v>15</v>
+      </c>
+      <c r="L185" t="s">
+        <v>15</v>
+      </c>
+      <c r="M185">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>2026</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186" t="s">
+        <v>35</v>
+      </c>
+      <c r="D186">
+        <v>429</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>69</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186" t="s">
+        <v>15</v>
+      </c>
+      <c r="K186" t="s">
+        <v>15</v>
+      </c>
+      <c r="L186" t="s">
+        <v>15</v>
+      </c>
+      <c r="M186">
+        <v>6364.3874999999998</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>2026</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
+        <v>36</v>
+      </c>
+      <c r="D187">
+        <v>101</v>
+      </c>
+      <c r="E187">
+        <v>2</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>68</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187" t="s">
+        <v>15</v>
+      </c>
+      <c r="K187" t="s">
+        <v>15</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M187" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>2026</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188" t="s">
+        <v>36</v>
+      </c>
+      <c r="D188">
+        <v>140</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>68</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188" t="s">
+        <v>15</v>
+      </c>
+      <c r="K188" t="s">
+        <v>15</v>
+      </c>
+      <c r="L188" t="s">
+        <v>15</v>
+      </c>
+      <c r="M188">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>2026</v>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+      <c r="C189" t="s">
+        <v>37</v>
+      </c>
+      <c r="D189">
+        <v>325</v>
+      </c>
+      <c r="E189">
+        <v>2</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>68</v>
+      </c>
+      <c r="I189">
+        <v>2</v>
+      </c>
+      <c r="J189" t="s">
+        <v>15</v>
+      </c>
+      <c r="K189" t="s">
+        <v>15</v>
+      </c>
+      <c r="L189" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M189" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>2026</v>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190" t="s">
+        <v>37</v>
+      </c>
+      <c r="D190">
+        <v>345</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190" t="s">
+        <v>14</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>68</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190" t="s">
+        <v>15</v>
+      </c>
+      <c r="K190" t="s">
+        <v>15</v>
+      </c>
+      <c r="L190" t="s">
+        <v>15</v>
+      </c>
+      <c r="M190">
+        <v>5863.5625</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>2026</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191" t="s">
+        <v>35</v>
+      </c>
+      <c r="D191">
+        <v>428</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191" t="s">
+        <v>14</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>68</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191" t="s">
+        <v>15</v>
+      </c>
+      <c r="K191" t="s">
+        <v>15</v>
+      </c>
+      <c r="L191" t="s">
+        <v>15</v>
+      </c>
+      <c r="M191">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>2026</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192" t="s">
+        <v>36</v>
+      </c>
+      <c r="D192">
+        <v>140</v>
+      </c>
+      <c r="E192">
+        <v>2</v>
+      </c>
+      <c r="F192" t="s">
+        <v>14</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>67</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192" t="s">
+        <v>15</v>
+      </c>
+      <c r="K192" t="s">
+        <v>15</v>
+      </c>
+      <c r="L192" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M192" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>2026</v>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193" t="s">
+        <v>36</v>
+      </c>
+      <c r="D193">
+        <v>140</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193" t="s">
+        <v>14</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>67</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193" t="s">
+        <v>15</v>
+      </c>
+      <c r="K193" t="s">
+        <v>15</v>
+      </c>
+      <c r="L193" t="s">
+        <v>15</v>
+      </c>
+      <c r="M193">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>2026</v>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194" t="s">
+        <v>35</v>
+      </c>
+      <c r="D194">
+        <v>427</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>14</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>67</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194" t="s">
+        <v>15</v>
+      </c>
+      <c r="K194" t="s">
+        <v>15</v>
+      </c>
+      <c r="L194" t="s">
+        <v>15</v>
+      </c>
+      <c r="M194">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>2026</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195" t="s">
+        <v>35</v>
+      </c>
+      <c r="D195">
+        <v>429</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>14</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>67</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195" t="s">
+        <v>15</v>
+      </c>
+      <c r="K195" t="s">
+        <v>15</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M195" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>2026</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>36</v>
+      </c>
+      <c r="D196">
+        <v>140</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196" t="s">
+        <v>14</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>65</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196" t="s">
+        <v>15</v>
+      </c>
+      <c r="K196" t="s">
+        <v>15</v>
+      </c>
+      <c r="L196" t="s">
+        <v>15</v>
+      </c>
+      <c r="M196">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>2026</v>
+      </c>
+      <c r="B197">
+        <v>2</v>
+      </c>
+      <c r="C197" t="s">
+        <v>35</v>
+      </c>
+      <c r="D197">
+        <v>427</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197" t="s">
+        <v>14</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>65</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197" t="s">
+        <v>15</v>
+      </c>
+      <c r="K197" t="s">
+        <v>15</v>
+      </c>
+      <c r="L197" t="s">
+        <v>15</v>
+      </c>
+      <c r="M197">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>2026</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+      <c r="C198" t="s">
+        <v>35</v>
+      </c>
+      <c r="D198">
+        <v>534</v>
+      </c>
+      <c r="E198">
+        <v>2</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>65</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198" t="s">
+        <v>15</v>
+      </c>
+      <c r="K198" t="s">
+        <v>15</v>
+      </c>
+      <c r="L198" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M198" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>2026</v>
+      </c>
+      <c r="B199">
+        <v>2</v>
+      </c>
+      <c r="C199" t="s">
+        <v>44</v>
+      </c>
+      <c r="D199">
+        <v>216</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>64</v>
+      </c>
+      <c r="I199">
+        <v>1</v>
+      </c>
+      <c r="J199" t="s">
+        <v>15</v>
+      </c>
+      <c r="K199" t="s">
+        <v>15</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M199" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>2026</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+      <c r="C200" t="s">
+        <v>35</v>
+      </c>
+      <c r="D200">
+        <v>428</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>64</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200" t="s">
+        <v>15</v>
+      </c>
+      <c r="K200" t="s">
+        <v>15</v>
+      </c>
+      <c r="L200" t="s">
+        <v>15</v>
+      </c>
+      <c r="M200">
+        <v>6394.5749999999998</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>2026</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+      <c r="C201" t="s">
+        <v>42</v>
+      </c>
+      <c r="D201">
+        <v>109</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="F201" t="s">
+        <v>14</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>63</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201" t="s">
+        <v>15</v>
+      </c>
+      <c r="K201" t="s">
+        <v>15</v>
+      </c>
+      <c r="L201" t="s">
+        <v>15</v>
+      </c>
+      <c r="M201">
+        <v>4993.5874999999996</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>2026</v>
+      </c>
+      <c r="B202">
+        <v>2</v>
+      </c>
+      <c r="C202" t="s">
+        <v>36</v>
+      </c>
+      <c r="D202">
+        <v>140</v>
+      </c>
+      <c r="E202">
+        <v>2</v>
+      </c>
+      <c r="F202" t="s">
+        <v>14</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>63</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202" t="s">
+        <v>15</v>
+      </c>
+      <c r="K202" t="s">
+        <v>15</v>
+      </c>
+      <c r="L202" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M202" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>2026</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+      <c r="C203" t="s">
+        <v>35</v>
+      </c>
+      <c r="D203">
+        <v>428</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
+      </c>
+      <c r="F203" t="s">
+        <v>14</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>63</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203" t="s">
+        <v>15</v>
+      </c>
+      <c r="K203" t="s">
+        <v>15</v>
+      </c>
+      <c r="L203" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M203" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>2026</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>36</v>
+      </c>
+      <c r="D204">
+        <v>140</v>
+      </c>
+      <c r="E204">
+        <v>1</v>
+      </c>
+      <c r="F204" t="s">
+        <v>14</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>62</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204" t="s">
+        <v>15</v>
+      </c>
+      <c r="K204" t="s">
+        <v>15</v>
+      </c>
+      <c r="L204" t="s">
+        <v>15</v>
+      </c>
+      <c r="M204">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>2026</v>
+      </c>
+      <c r="B205">
+        <v>2</v>
+      </c>
+      <c r="C205" t="s">
+        <v>35</v>
+      </c>
+      <c r="D205">
+        <v>427</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="F205" t="s">
+        <v>14</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>62</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205" t="s">
+        <v>15</v>
+      </c>
+      <c r="K205" t="s">
+        <v>15</v>
+      </c>
+      <c r="L205" t="s">
+        <v>15</v>
+      </c>
+      <c r="M205">
+        <v>4490.4624999999996</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>2026</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206" t="s">
+        <v>36</v>
+      </c>
+      <c r="D206">
+        <v>140</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
+      </c>
+      <c r="F206" t="s">
+        <v>14</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>60</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206" t="s">
+        <v>15</v>
+      </c>
+      <c r="K206" t="s">
+        <v>15</v>
+      </c>
+      <c r="L206" t="s">
+        <v>15</v>
+      </c>
+      <c r="M206">
+        <v>5938.6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>2026</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207" t="s">
+        <v>37</v>
+      </c>
+      <c r="D207">
+        <v>325</v>
+      </c>
+      <c r="E207">
+        <v>2</v>
+      </c>
+      <c r="F207" t="s">
+        <v>14</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>58</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207" t="s">
+        <v>15</v>
+      </c>
+      <c r="K207" t="s">
+        <v>15</v>
+      </c>
+      <c r="L207" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M207" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>2026</v>
+      </c>
+      <c r="B208">
+        <v>2</v>
+      </c>
+      <c r="C208" t="s">
+        <v>42</v>
+      </c>
+      <c r="D208">
+        <v>109</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208" t="s">
+        <v>14</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>57</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208" t="s">
+        <v>15</v>
+      </c>
+      <c r="K208" t="s">
+        <v>15</v>
+      </c>
+      <c r="L208" t="s">
+        <v>15</v>
+      </c>
+      <c r="M208">
+        <v>4993.5874999999996</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>2026</v>
+      </c>
+      <c r="B209">
+        <v>2</v>
+      </c>
+      <c r="C209" t="s">
+        <v>35</v>
+      </c>
+      <c r="D209">
+        <v>429</v>
+      </c>
+      <c r="E209">
+        <v>2</v>
+      </c>
+      <c r="F209" t="s">
+        <v>14</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>53</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209" t="s">
+        <v>15</v>
+      </c>
+      <c r="K209" t="s">
+        <v>15</v>
+      </c>
+      <c r="L209" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M209" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_raw/smelt/SFBS_2026.xlsx
+++ b/data_raw/smelt/SFBS_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/lmccormick_usbr_gov/Documents/Documents/Research/R/samt_smt_assessments/data_raw/smelt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B39F03-9EBE-4F56-B6F5-4D4EC5D7AE55}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E67F16C5-6AC4-4AF1-9D09-1FEFF4631871}"/>
   <bookViews>
-    <workbookView xWindow="12192" yWindow="-14112" windowWidth="22332" windowHeight="12300" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
+    <workbookView xWindow="11520" yWindow="-14208" windowWidth="21192" windowHeight="11460" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="54">
   <si>
     <t>Year</t>
   </si>
@@ -174,6 +174,30 @@
   </si>
   <si>
     <t>697.1799962222576</t>
+  </si>
+  <si>
+    <t>2026-03-11T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T00:00:00Z</t>
+  </si>
+  <si>
+    <t>confirm with Kenji?</t>
+  </si>
+  <si>
+    <t>pieces</t>
+  </si>
+  <si>
+    <t>2026-03-04T00:00:00Z</t>
+  </si>
+  <si>
+    <t>646.4759879112244</t>
+  </si>
+  <si>
+    <t>2026-03-03T00:00:00Z</t>
   </si>
 </sst>
 </file>
@@ -550,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84FFA20-E1FB-43B3-8FA5-E079A449C1F1}">
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M242"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -9119,6 +9143,1359 @@
         <v>15</v>
       </c>
     </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>2026</v>
+      </c>
+      <c r="B210">
+        <v>3</v>
+      </c>
+      <c r="C210" t="s">
+        <v>46</v>
+      </c>
+      <c r="D210">
+        <v>107</v>
+      </c>
+      <c r="E210">
+        <v>2</v>
+      </c>
+      <c r="F210" t="s">
+        <v>14</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>51</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210" t="s">
+        <v>15</v>
+      </c>
+      <c r="K210" t="s">
+        <v>15</v>
+      </c>
+      <c r="L210" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M210" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>2026</v>
+      </c>
+      <c r="B211">
+        <v>3</v>
+      </c>
+      <c r="C211" t="s">
+        <v>47</v>
+      </c>
+      <c r="D211">
+        <v>109</v>
+      </c>
+      <c r="E211">
+        <v>2</v>
+      </c>
+      <c r="F211" t="s">
+        <v>14</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>74</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211" t="s">
+        <v>15</v>
+      </c>
+      <c r="K211" t="s">
+        <v>15</v>
+      </c>
+      <c r="L211" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M211" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>2026</v>
+      </c>
+      <c r="B212">
+        <v>3</v>
+      </c>
+      <c r="C212" t="s">
+        <v>47</v>
+      </c>
+      <c r="D212">
+        <v>109</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+      <c r="F212" t="s">
+        <v>14</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>77</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212" t="s">
+        <v>15</v>
+      </c>
+      <c r="K212" t="s">
+        <v>15</v>
+      </c>
+      <c r="L212" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M212" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>2026</v>
+      </c>
+      <c r="B213">
+        <v>3</v>
+      </c>
+      <c r="C213" t="s">
+        <v>47</v>
+      </c>
+      <c r="D213">
+        <v>109</v>
+      </c>
+      <c r="E213">
+        <v>2</v>
+      </c>
+      <c r="F213" t="s">
+        <v>14</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>79</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213" t="s">
+        <v>15</v>
+      </c>
+      <c r="K213" t="s">
+        <v>15</v>
+      </c>
+      <c r="L213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M213" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>2026</v>
+      </c>
+      <c r="B214">
+        <v>3</v>
+      </c>
+      <c r="C214" t="s">
+        <v>47</v>
+      </c>
+      <c r="D214">
+        <v>109</v>
+      </c>
+      <c r="E214">
+        <v>2</v>
+      </c>
+      <c r="F214" t="s">
+        <v>14</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>69</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214" t="s">
+        <v>15</v>
+      </c>
+      <c r="K214" t="s">
+        <v>15</v>
+      </c>
+      <c r="L214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M214" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>2026</v>
+      </c>
+      <c r="B215">
+        <v>3</v>
+      </c>
+      <c r="C215" t="s">
+        <v>47</v>
+      </c>
+      <c r="D215">
+        <v>109</v>
+      </c>
+      <c r="E215">
+        <v>2</v>
+      </c>
+      <c r="F215" t="s">
+        <v>14</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>70</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215" t="s">
+        <v>15</v>
+      </c>
+      <c r="K215" t="s">
+        <v>15</v>
+      </c>
+      <c r="L215" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M215" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>2026</v>
+      </c>
+      <c r="B216">
+        <v>3</v>
+      </c>
+      <c r="C216" t="s">
+        <v>48</v>
+      </c>
+      <c r="D216">
+        <v>320</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216" t="s">
+        <v>14</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>75</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216" t="s">
+        <v>15</v>
+      </c>
+      <c r="K216" t="s">
+        <v>15</v>
+      </c>
+      <c r="L216" t="s">
+        <v>15</v>
+      </c>
+      <c r="M216">
+        <v>6064.5249999999996</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>2026</v>
+      </c>
+      <c r="B217">
+        <v>3</v>
+      </c>
+      <c r="C217" t="s">
+        <v>48</v>
+      </c>
+      <c r="D217">
+        <v>322</v>
+      </c>
+      <c r="E217">
+        <v>2</v>
+      </c>
+      <c r="F217" t="s">
+        <v>14</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>67</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217" t="s">
+        <v>15</v>
+      </c>
+      <c r="K217" t="s">
+        <v>15</v>
+      </c>
+      <c r="L217" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M217" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>2026</v>
+      </c>
+      <c r="B218">
+        <v>3</v>
+      </c>
+      <c r="C218" t="s">
+        <v>48</v>
+      </c>
+      <c r="D218">
+        <v>323</v>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+      <c r="F218" t="s">
+        <v>14</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+      <c r="H218">
+        <v>77</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218" t="s">
+        <v>15</v>
+      </c>
+      <c r="K218" t="s">
+        <v>15</v>
+      </c>
+      <c r="L218" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M218" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>2026</v>
+      </c>
+      <c r="B219">
+        <v>3</v>
+      </c>
+      <c r="C219" t="s">
+        <v>48</v>
+      </c>
+      <c r="D219">
+        <v>323</v>
+      </c>
+      <c r="E219">
+        <v>2</v>
+      </c>
+      <c r="F219" t="s">
+        <v>14</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>78</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219" t="s">
+        <v>15</v>
+      </c>
+      <c r="K219" t="s">
+        <v>15</v>
+      </c>
+      <c r="L219" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M219" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>2026</v>
+      </c>
+      <c r="B220">
+        <v>3</v>
+      </c>
+      <c r="C220" t="s">
+        <v>48</v>
+      </c>
+      <c r="D220">
+        <v>325</v>
+      </c>
+      <c r="E220">
+        <v>2</v>
+      </c>
+      <c r="F220" t="s">
+        <v>14</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>85</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220" t="s">
+        <v>15</v>
+      </c>
+      <c r="K220" t="s">
+        <v>15</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M220" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>2026</v>
+      </c>
+      <c r="B221">
+        <v>3</v>
+      </c>
+      <c r="C221" t="s">
+        <v>48</v>
+      </c>
+      <c r="D221">
+        <v>325</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+      <c r="F221" t="s">
+        <v>14</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>77</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221" t="s">
+        <v>15</v>
+      </c>
+      <c r="K221" t="s">
+        <v>49</v>
+      </c>
+      <c r="L221" t="s">
+        <v>15</v>
+      </c>
+      <c r="M221">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>2026</v>
+      </c>
+      <c r="B222">
+        <v>3</v>
+      </c>
+      <c r="C222" t="s">
+        <v>48</v>
+      </c>
+      <c r="D222">
+        <v>325</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+      <c r="F222" t="s">
+        <v>14</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>58</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222" t="s">
+        <v>15</v>
+      </c>
+      <c r="K222" t="s">
+        <v>49</v>
+      </c>
+      <c r="L222" t="s">
+        <v>15</v>
+      </c>
+      <c r="M222">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>2026</v>
+      </c>
+      <c r="B223">
+        <v>3</v>
+      </c>
+      <c r="C223" t="s">
+        <v>48</v>
+      </c>
+      <c r="D223">
+        <v>325</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="F223" t="s">
+        <v>14</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>62</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223" t="s">
+        <v>15</v>
+      </c>
+      <c r="K223" t="s">
+        <v>49</v>
+      </c>
+      <c r="L223" t="s">
+        <v>15</v>
+      </c>
+      <c r="M223">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>2026</v>
+      </c>
+      <c r="B224">
+        <v>3</v>
+      </c>
+      <c r="C224" t="s">
+        <v>48</v>
+      </c>
+      <c r="D224">
+        <v>325</v>
+      </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
+      <c r="F224" t="s">
+        <v>14</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>69</v>
+      </c>
+      <c r="I224">
+        <v>2</v>
+      </c>
+      <c r="J224" t="s">
+        <v>15</v>
+      </c>
+      <c r="K224" t="s">
+        <v>15</v>
+      </c>
+      <c r="L224" t="s">
+        <v>15</v>
+      </c>
+      <c r="M224">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>2026</v>
+      </c>
+      <c r="B225">
+        <v>3</v>
+      </c>
+      <c r="C225" t="s">
+        <v>48</v>
+      </c>
+      <c r="D225">
+        <v>325</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+      <c r="F225" t="s">
+        <v>14</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>63</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225" t="s">
+        <v>15</v>
+      </c>
+      <c r="K225" t="s">
+        <v>15</v>
+      </c>
+      <c r="L225" t="s">
+        <v>15</v>
+      </c>
+      <c r="M225">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>2026</v>
+      </c>
+      <c r="B226">
+        <v>3</v>
+      </c>
+      <c r="C226" t="s">
+        <v>48</v>
+      </c>
+      <c r="D226">
+        <v>325</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+      <c r="F226" t="s">
+        <v>14</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>62</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226" t="s">
+        <v>15</v>
+      </c>
+      <c r="K226" t="s">
+        <v>15</v>
+      </c>
+      <c r="L226" t="s">
+        <v>15</v>
+      </c>
+      <c r="M226">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>2026</v>
+      </c>
+      <c r="B227">
+        <v>3</v>
+      </c>
+      <c r="C227" t="s">
+        <v>48</v>
+      </c>
+      <c r="D227">
+        <v>325</v>
+      </c>
+      <c r="E227">
+        <v>1</v>
+      </c>
+      <c r="F227" t="s">
+        <v>14</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>65</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227" t="s">
+        <v>15</v>
+      </c>
+      <c r="K227" t="s">
+        <v>15</v>
+      </c>
+      <c r="L227" t="s">
+        <v>15</v>
+      </c>
+      <c r="M227">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>2026</v>
+      </c>
+      <c r="B228">
+        <v>3</v>
+      </c>
+      <c r="C228" t="s">
+        <v>48</v>
+      </c>
+      <c r="D228">
+        <v>325</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
+      <c r="F228" t="s">
+        <v>14</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>73</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228" t="s">
+        <v>15</v>
+      </c>
+      <c r="K228" t="s">
+        <v>15</v>
+      </c>
+      <c r="L228" t="s">
+        <v>15</v>
+      </c>
+      <c r="M228">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>2026</v>
+      </c>
+      <c r="B229">
+        <v>3</v>
+      </c>
+      <c r="C229" t="s">
+        <v>48</v>
+      </c>
+      <c r="D229">
+        <v>325</v>
+      </c>
+      <c r="E229">
+        <v>1</v>
+      </c>
+      <c r="F229" t="s">
+        <v>14</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>82</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229" t="s">
+        <v>15</v>
+      </c>
+      <c r="K229" t="s">
+        <v>15</v>
+      </c>
+      <c r="L229" t="s">
+        <v>15</v>
+      </c>
+      <c r="M229">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>2026</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230" t="s">
+        <v>48</v>
+      </c>
+      <c r="D230">
+        <v>325</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+      <c r="F230" t="s">
+        <v>14</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>78</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230" t="s">
+        <v>15</v>
+      </c>
+      <c r="K230" t="s">
+        <v>15</v>
+      </c>
+      <c r="L230" t="s">
+        <v>15</v>
+      </c>
+      <c r="M230">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>2026</v>
+      </c>
+      <c r="B231">
+        <v>3</v>
+      </c>
+      <c r="C231" t="s">
+        <v>48</v>
+      </c>
+      <c r="D231">
+        <v>325</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231" t="s">
+        <v>14</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>74</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231" t="s">
+        <v>15</v>
+      </c>
+      <c r="K231" t="s">
+        <v>15</v>
+      </c>
+      <c r="L231" t="s">
+        <v>15</v>
+      </c>
+      <c r="M231">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>2026</v>
+      </c>
+      <c r="B232">
+        <v>3</v>
+      </c>
+      <c r="C232" t="s">
+        <v>48</v>
+      </c>
+      <c r="D232">
+        <v>325</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
+      <c r="F232" t="s">
+        <v>14</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>80</v>
+      </c>
+      <c r="I232">
+        <v>2</v>
+      </c>
+      <c r="J232" t="s">
+        <v>15</v>
+      </c>
+      <c r="K232" t="s">
+        <v>15</v>
+      </c>
+      <c r="L232" t="s">
+        <v>15</v>
+      </c>
+      <c r="M232">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>2026</v>
+      </c>
+      <c r="B233">
+        <v>3</v>
+      </c>
+      <c r="C233" t="s">
+        <v>48</v>
+      </c>
+      <c r="D233">
+        <v>325</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
+      <c r="F233" t="s">
+        <v>14</v>
+      </c>
+      <c r="G233" t="s">
+        <v>15</v>
+      </c>
+      <c r="H233" t="s">
+        <v>15</v>
+      </c>
+      <c r="I233" t="s">
+        <v>15</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233" t="s">
+        <v>50</v>
+      </c>
+      <c r="L233" t="s">
+        <v>15</v>
+      </c>
+      <c r="M233">
+        <v>9940.8875000000007</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>2026</v>
+      </c>
+      <c r="B234">
+        <v>3</v>
+      </c>
+      <c r="C234" t="s">
+        <v>48</v>
+      </c>
+      <c r="D234">
+        <v>345</v>
+      </c>
+      <c r="E234">
+        <v>2</v>
+      </c>
+      <c r="F234" t="s">
+        <v>14</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>83</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234" t="s">
+        <v>15</v>
+      </c>
+      <c r="K234" t="s">
+        <v>15</v>
+      </c>
+      <c r="L234" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M234" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>2026</v>
+      </c>
+      <c r="B235">
+        <v>3</v>
+      </c>
+      <c r="C235" t="s">
+        <v>48</v>
+      </c>
+      <c r="D235">
+        <v>346</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="F235" t="s">
+        <v>14</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>78</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235" t="s">
+        <v>15</v>
+      </c>
+      <c r="K235" t="s">
+        <v>15</v>
+      </c>
+      <c r="L235" t="s">
+        <v>15</v>
+      </c>
+      <c r="M235">
+        <v>4890.375</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>2026</v>
+      </c>
+      <c r="B236">
+        <v>3</v>
+      </c>
+      <c r="C236" t="s">
+        <v>51</v>
+      </c>
+      <c r="D236">
+        <v>427</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236" t="s">
+        <v>14</v>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>89</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236" t="s">
+        <v>15</v>
+      </c>
+      <c r="K236" t="s">
+        <v>15</v>
+      </c>
+      <c r="L236" t="s">
+        <v>15</v>
+      </c>
+      <c r="M236">
+        <v>6860.3249999999998</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>2026</v>
+      </c>
+      <c r="B237">
+        <v>3</v>
+      </c>
+      <c r="C237" t="s">
+        <v>51</v>
+      </c>
+      <c r="D237">
+        <v>427</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+      <c r="F237" t="s">
+        <v>14</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>90</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237" t="s">
+        <v>15</v>
+      </c>
+      <c r="K237" t="s">
+        <v>15</v>
+      </c>
+      <c r="L237" t="s">
+        <v>15</v>
+      </c>
+      <c r="M237">
+        <v>6860.3249999999998</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>2026</v>
+      </c>
+      <c r="B238">
+        <v>3</v>
+      </c>
+      <c r="C238" t="s">
+        <v>51</v>
+      </c>
+      <c r="D238">
+        <v>427</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="F238" t="s">
+        <v>14</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>63</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238" t="s">
+        <v>15</v>
+      </c>
+      <c r="K238" t="s">
+        <v>15</v>
+      </c>
+      <c r="L238" t="s">
+        <v>15</v>
+      </c>
+      <c r="M238">
+        <v>6860.3249999999998</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>2026</v>
+      </c>
+      <c r="B239">
+        <v>3</v>
+      </c>
+      <c r="C239" t="s">
+        <v>51</v>
+      </c>
+      <c r="D239">
+        <v>429</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+      <c r="F239" t="s">
+        <v>14</v>
+      </c>
+      <c r="G239">
+        <v>0</v>
+      </c>
+      <c r="H239">
+        <v>83</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239" t="s">
+        <v>15</v>
+      </c>
+      <c r="K239" t="s">
+        <v>15</v>
+      </c>
+      <c r="L239" t="s">
+        <v>15</v>
+      </c>
+      <c r="M239">
+        <v>6633.4875000000002</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>2026</v>
+      </c>
+      <c r="B240">
+        <v>3</v>
+      </c>
+      <c r="C240" t="s">
+        <v>51</v>
+      </c>
+      <c r="D240">
+        <v>432</v>
+      </c>
+      <c r="E240">
+        <v>2</v>
+      </c>
+      <c r="F240" t="s">
+        <v>14</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240">
+        <v>88</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240" t="s">
+        <v>15</v>
+      </c>
+      <c r="K240" t="s">
+        <v>15</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M240" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>2026</v>
+      </c>
+      <c r="B241">
+        <v>3</v>
+      </c>
+      <c r="C241" t="s">
+        <v>51</v>
+      </c>
+      <c r="D241">
+        <v>535</v>
+      </c>
+      <c r="E241">
+        <v>1</v>
+      </c>
+      <c r="F241" t="s">
+        <v>14</v>
+      </c>
+      <c r="G241">
+        <v>0</v>
+      </c>
+      <c r="H241">
+        <v>91</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241" t="s">
+        <v>15</v>
+      </c>
+      <c r="K241" t="s">
+        <v>15</v>
+      </c>
+      <c r="L241" t="s">
+        <v>15</v>
+      </c>
+      <c r="M241">
+        <v>5512.2375000000002</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>2026</v>
+      </c>
+      <c r="B242">
+        <v>3</v>
+      </c>
+      <c r="C242" t="s">
+        <v>53</v>
+      </c>
+      <c r="D242">
+        <v>736</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="F242" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242">
+        <v>0</v>
+      </c>
+      <c r="H242">
+        <v>75</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242" t="s">
+        <v>15</v>
+      </c>
+      <c r="K242" t="s">
+        <v>15</v>
+      </c>
+      <c r="L242" t="s">
+        <v>15</v>
+      </c>
+      <c r="M242">
+        <v>6522.2250000000004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_raw/smelt/SFBS_2026.xlsx
+++ b/data_raw/smelt/SFBS_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/lmccormick_usbr_gov/Documents/Documents/Research/R/samt_smt_assessments/data_raw/smelt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E67F16C5-6AC4-4AF1-9D09-1FEFF4631871}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1934A60-1DB7-4076-9434-11CD7BC4D879}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="-14208" windowWidth="21192" windowHeight="11460" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
+    <workbookView xWindow="-11688" yWindow="-13404" windowWidth="21192" windowHeight="11460" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="54">
   <si>
     <t>Year</t>
   </si>
@@ -576,6 +576,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84FFA20-E1FB-43B3-8FA5-E079A449C1F1}">
   <dimension ref="A1:M242"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -637,6 +640,9 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="H2" t="s">
         <v>15</v>
       </c>
@@ -10104,9 +10110,6 @@
       </c>
       <c r="F233" t="s">
         <v>14</v>
-      </c>
-      <c r="G233" t="s">
-        <v>15</v>
       </c>
       <c r="H233" t="s">
         <v>15</v>

--- a/data_raw/smelt/SFBS_2026.xlsx
+++ b/data_raw/smelt/SFBS_2026.xlsx
@@ -10502,4 +10502,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data_raw/smelt/SFBS_2026.xlsx
+++ b/data_raw/smelt/SFBS_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/lmccormick_usbr_gov/Documents/Documents/Research/R/samt_smt_assessments/data_raw/smelt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1934A60-1DB7-4076-9434-11CD7BC4D879}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{47B3780D-476C-45E1-BD2A-9CFBAA023493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{064AE317-D451-45EF-A6F0-F8082C2E8C69}"/>
   <bookViews>
-    <workbookView xWindow="-11688" yWindow="-13404" windowWidth="21192" windowHeight="11460" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
+    <workbookView xWindow="-16284" yWindow="-15528" windowWidth="23040" windowHeight="12120" xr2:uid="{9CCD3A7D-A9FF-4AB3-9F66-F845580CB748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="65">
   <si>
     <t>Year</t>
   </si>
@@ -198,6 +198,39 @@
   </si>
   <si>
     <t>2026-03-03T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-04-13T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-04-09T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-04-08T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-04-07T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-05-11T00:00:00Z</t>
+  </si>
+  <si>
+    <t>570.4200226664543</t>
+  </si>
+  <si>
+    <t>2026-05-06T00:00:00Z</t>
+  </si>
+  <si>
+    <t>2026-05-05T00:00:00Z</t>
+  </si>
+  <si>
+    <t>Plus count due to half bodies</t>
+  </si>
+  <si>
+    <t>836.6159954667091</t>
+  </si>
+  <si>
+    <t>Didn't state why?</t>
   </si>
 </sst>
 </file>
@@ -574,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84FFA20-E1FB-43B3-8FA5-E079A449C1F1}">
-  <dimension ref="A1:M242"/>
+  <dimension ref="A1:M428"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -10497,6 +10530,7614 @@
       </c>
       <c r="M242">
         <v>6522.2250000000004</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>2026</v>
+      </c>
+      <c r="B243">
+        <v>4</v>
+      </c>
+      <c r="C243" t="s">
+        <v>54</v>
+      </c>
+      <c r="D243">
+        <v>213</v>
+      </c>
+      <c r="E243">
+        <v>2</v>
+      </c>
+      <c r="F243" t="s">
+        <v>14</v>
+      </c>
+      <c r="G243">
+        <v>0</v>
+      </c>
+      <c r="H243">
+        <v>81</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243" t="s">
+        <v>15</v>
+      </c>
+      <c r="K243" t="s">
+        <v>15</v>
+      </c>
+      <c r="L243">
+        <v>988.72802039999999</v>
+      </c>
+      <c r="M243" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>2026</v>
+      </c>
+      <c r="B244">
+        <v>4</v>
+      </c>
+      <c r="C244" t="s">
+        <v>54</v>
+      </c>
+      <c r="D244">
+        <v>213</v>
+      </c>
+      <c r="E244">
+        <v>2</v>
+      </c>
+      <c r="F244" t="s">
+        <v>14</v>
+      </c>
+      <c r="G244">
+        <v>0</v>
+      </c>
+      <c r="H244">
+        <v>85</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244" t="s">
+        <v>15</v>
+      </c>
+      <c r="K244" t="s">
+        <v>15</v>
+      </c>
+      <c r="L244">
+        <v>988.72802039999999</v>
+      </c>
+      <c r="M244" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>2026</v>
+      </c>
+      <c r="B245">
+        <v>4</v>
+      </c>
+      <c r="C245" t="s">
+        <v>54</v>
+      </c>
+      <c r="D245">
+        <v>244</v>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+      <c r="F245" t="s">
+        <v>14</v>
+      </c>
+      <c r="G245">
+        <v>0</v>
+      </c>
+      <c r="H245">
+        <v>46</v>
+      </c>
+      <c r="I245">
+        <v>1</v>
+      </c>
+      <c r="J245" t="s">
+        <v>15</v>
+      </c>
+      <c r="K245" t="s">
+        <v>15</v>
+      </c>
+      <c r="L245">
+        <v>988.72802039999999</v>
+      </c>
+      <c r="M245" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>2026</v>
+      </c>
+      <c r="B246">
+        <v>4</v>
+      </c>
+      <c r="C246" t="s">
+        <v>55</v>
+      </c>
+      <c r="D246">
+        <v>345</v>
+      </c>
+      <c r="E246">
+        <v>1</v>
+      </c>
+      <c r="F246" t="s">
+        <v>14</v>
+      </c>
+      <c r="G246">
+        <v>0</v>
+      </c>
+      <c r="H246">
+        <v>42</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246" t="s">
+        <v>15</v>
+      </c>
+      <c r="K246" t="s">
+        <v>15</v>
+      </c>
+      <c r="L246" t="s">
+        <v>15</v>
+      </c>
+      <c r="M246">
+        <v>5112.8999999999996</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>2026</v>
+      </c>
+      <c r="B247">
+        <v>4</v>
+      </c>
+      <c r="C247" t="s">
+        <v>55</v>
+      </c>
+      <c r="D247">
+        <v>346</v>
+      </c>
+      <c r="E247">
+        <v>2</v>
+      </c>
+      <c r="F247" t="s">
+        <v>14</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>86</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247" t="s">
+        <v>15</v>
+      </c>
+      <c r="K247" t="s">
+        <v>15</v>
+      </c>
+      <c r="L247">
+        <v>899.99602949999996</v>
+      </c>
+      <c r="M247" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>2026</v>
+      </c>
+      <c r="B248">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>55</v>
+      </c>
+      <c r="D248">
+        <v>346</v>
+      </c>
+      <c r="E248">
+        <v>2</v>
+      </c>
+      <c r="F248" t="s">
+        <v>14</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
+      </c>
+      <c r="H248">
+        <v>84</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248" t="s">
+        <v>15</v>
+      </c>
+      <c r="K248" t="s">
+        <v>15</v>
+      </c>
+      <c r="L248">
+        <v>899.99602949999996</v>
+      </c>
+      <c r="M248" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>2026</v>
+      </c>
+      <c r="B249">
+        <v>4</v>
+      </c>
+      <c r="C249" t="s">
+        <v>55</v>
+      </c>
+      <c r="D249">
+        <v>346</v>
+      </c>
+      <c r="E249">
+        <v>2</v>
+      </c>
+      <c r="F249" t="s">
+        <v>14</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
+      </c>
+      <c r="H249">
+        <v>75</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249" t="s">
+        <v>15</v>
+      </c>
+      <c r="K249" t="s">
+        <v>15</v>
+      </c>
+      <c r="L249">
+        <v>899.99602949999996</v>
+      </c>
+      <c r="M249" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>2026</v>
+      </c>
+      <c r="B250">
+        <v>4</v>
+      </c>
+      <c r="C250" t="s">
+        <v>55</v>
+      </c>
+      <c r="D250">
+        <v>346</v>
+      </c>
+      <c r="E250">
+        <v>2</v>
+      </c>
+      <c r="F250" t="s">
+        <v>14</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>40</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250" t="s">
+        <v>15</v>
+      </c>
+      <c r="K250" t="s">
+        <v>15</v>
+      </c>
+      <c r="L250">
+        <v>899.99602949999996</v>
+      </c>
+      <c r="M250" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>2026</v>
+      </c>
+      <c r="B251">
+        <v>4</v>
+      </c>
+      <c r="C251" t="s">
+        <v>55</v>
+      </c>
+      <c r="D251">
+        <v>346</v>
+      </c>
+      <c r="E251">
+        <v>2</v>
+      </c>
+      <c r="F251" t="s">
+        <v>14</v>
+      </c>
+      <c r="G251">
+        <v>8</v>
+      </c>
+      <c r="H251">
+        <v>36</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251" t="s">
+        <v>15</v>
+      </c>
+      <c r="K251" t="s">
+        <v>15</v>
+      </c>
+      <c r="L251">
+        <v>899.99602949999996</v>
+      </c>
+      <c r="M251" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>2026</v>
+      </c>
+      <c r="B252">
+        <v>4</v>
+      </c>
+      <c r="C252" t="s">
+        <v>56</v>
+      </c>
+      <c r="D252">
+        <v>427</v>
+      </c>
+      <c r="E252">
+        <v>1</v>
+      </c>
+      <c r="F252" t="s">
+        <v>14</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>88</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252" t="s">
+        <v>15</v>
+      </c>
+      <c r="K252" t="s">
+        <v>15</v>
+      </c>
+      <c r="L252" t="s">
+        <v>15</v>
+      </c>
+      <c r="M252">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>2026</v>
+      </c>
+      <c r="B253">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>56</v>
+      </c>
+      <c r="D253">
+        <v>427</v>
+      </c>
+      <c r="E253">
+        <v>1</v>
+      </c>
+      <c r="F253" t="s">
+        <v>14</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>84</v>
+      </c>
+      <c r="I253">
+        <v>2</v>
+      </c>
+      <c r="J253" t="s">
+        <v>15</v>
+      </c>
+      <c r="K253" t="s">
+        <v>15</v>
+      </c>
+      <c r="L253" t="s">
+        <v>15</v>
+      </c>
+      <c r="M253">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>2026</v>
+      </c>
+      <c r="B254">
+        <v>4</v>
+      </c>
+      <c r="C254" t="s">
+        <v>56</v>
+      </c>
+      <c r="D254">
+        <v>427</v>
+      </c>
+      <c r="E254">
+        <v>1</v>
+      </c>
+      <c r="F254" t="s">
+        <v>14</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>67</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254" t="s">
+        <v>15</v>
+      </c>
+      <c r="K254" t="s">
+        <v>15</v>
+      </c>
+      <c r="L254" t="s">
+        <v>15</v>
+      </c>
+      <c r="M254">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>2026</v>
+      </c>
+      <c r="B255">
+        <v>4</v>
+      </c>
+      <c r="C255" t="s">
+        <v>56</v>
+      </c>
+      <c r="D255">
+        <v>427</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255" t="s">
+        <v>14</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>87</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255" t="s">
+        <v>15</v>
+      </c>
+      <c r="K255" t="s">
+        <v>15</v>
+      </c>
+      <c r="L255" t="s">
+        <v>15</v>
+      </c>
+      <c r="M255">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>2026</v>
+      </c>
+      <c r="B256">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>56</v>
+      </c>
+      <c r="D256">
+        <v>427</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+      <c r="F256" t="s">
+        <v>14</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>70</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256" t="s">
+        <v>15</v>
+      </c>
+      <c r="K256" t="s">
+        <v>15</v>
+      </c>
+      <c r="L256" t="s">
+        <v>15</v>
+      </c>
+      <c r="M256">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>2026</v>
+      </c>
+      <c r="B257">
+        <v>4</v>
+      </c>
+      <c r="C257" t="s">
+        <v>56</v>
+      </c>
+      <c r="D257">
+        <v>427</v>
+      </c>
+      <c r="E257">
+        <v>1</v>
+      </c>
+      <c r="F257" t="s">
+        <v>14</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>74</v>
+      </c>
+      <c r="I257">
+        <v>1</v>
+      </c>
+      <c r="J257" t="s">
+        <v>15</v>
+      </c>
+      <c r="K257" t="s">
+        <v>15</v>
+      </c>
+      <c r="L257" t="s">
+        <v>15</v>
+      </c>
+      <c r="M257">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>2026</v>
+      </c>
+      <c r="B258">
+        <v>4</v>
+      </c>
+      <c r="C258" t="s">
+        <v>56</v>
+      </c>
+      <c r="D258">
+        <v>427</v>
+      </c>
+      <c r="E258">
+        <v>1</v>
+      </c>
+      <c r="F258" t="s">
+        <v>14</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>90</v>
+      </c>
+      <c r="I258">
+        <v>1</v>
+      </c>
+      <c r="J258" t="s">
+        <v>15</v>
+      </c>
+      <c r="K258" t="s">
+        <v>15</v>
+      </c>
+      <c r="L258" t="s">
+        <v>15</v>
+      </c>
+      <c r="M258">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>2026</v>
+      </c>
+      <c r="B259">
+        <v>4</v>
+      </c>
+      <c r="C259" t="s">
+        <v>56</v>
+      </c>
+      <c r="D259">
+        <v>427</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+      <c r="F259" t="s">
+        <v>14</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>77</v>
+      </c>
+      <c r="I259">
+        <v>1</v>
+      </c>
+      <c r="J259" t="s">
+        <v>15</v>
+      </c>
+      <c r="K259" t="s">
+        <v>15</v>
+      </c>
+      <c r="L259" t="s">
+        <v>15</v>
+      </c>
+      <c r="M259">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>2026</v>
+      </c>
+      <c r="B260">
+        <v>4</v>
+      </c>
+      <c r="C260" t="s">
+        <v>56</v>
+      </c>
+      <c r="D260">
+        <v>427</v>
+      </c>
+      <c r="E260">
+        <v>1</v>
+      </c>
+      <c r="F260" t="s">
+        <v>14</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>76</v>
+      </c>
+      <c r="I260">
+        <v>1</v>
+      </c>
+      <c r="J260" t="s">
+        <v>15</v>
+      </c>
+      <c r="K260" t="s">
+        <v>15</v>
+      </c>
+      <c r="L260" t="s">
+        <v>15</v>
+      </c>
+      <c r="M260">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>2026</v>
+      </c>
+      <c r="B261">
+        <v>4</v>
+      </c>
+      <c r="C261" t="s">
+        <v>56</v>
+      </c>
+      <c r="D261">
+        <v>427</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+      <c r="F261" t="s">
+        <v>14</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>92</v>
+      </c>
+      <c r="I261">
+        <v>1</v>
+      </c>
+      <c r="J261" t="s">
+        <v>15</v>
+      </c>
+      <c r="K261" t="s">
+        <v>15</v>
+      </c>
+      <c r="L261" t="s">
+        <v>15</v>
+      </c>
+      <c r="M261">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>2026</v>
+      </c>
+      <c r="B262">
+        <v>4</v>
+      </c>
+      <c r="C262" t="s">
+        <v>56</v>
+      </c>
+      <c r="D262">
+        <v>427</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>80</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262" t="s">
+        <v>15</v>
+      </c>
+      <c r="K262" t="s">
+        <v>15</v>
+      </c>
+      <c r="L262" t="s">
+        <v>15</v>
+      </c>
+      <c r="M262">
+        <v>3192.4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>2026</v>
+      </c>
+      <c r="B263">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>56</v>
+      </c>
+      <c r="D263">
+        <v>428</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
+      <c r="F263" t="s">
+        <v>14</v>
+      </c>
+      <c r="G263">
+        <v>8</v>
+      </c>
+      <c r="H263">
+        <v>34</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263" t="s">
+        <v>15</v>
+      </c>
+      <c r="K263" t="s">
+        <v>15</v>
+      </c>
+      <c r="L263" t="s">
+        <v>15</v>
+      </c>
+      <c r="M263">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>2026</v>
+      </c>
+      <c r="B264">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>56</v>
+      </c>
+      <c r="D264">
+        <v>428</v>
+      </c>
+      <c r="E264">
+        <v>2</v>
+      </c>
+      <c r="F264" t="s">
+        <v>14</v>
+      </c>
+      <c r="G264">
+        <v>8</v>
+      </c>
+      <c r="H264">
+        <v>26</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264" t="s">
+        <v>15</v>
+      </c>
+      <c r="K264" t="s">
+        <v>15</v>
+      </c>
+      <c r="L264">
+        <v>570.4200227</v>
+      </c>
+      <c r="M264" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>2026</v>
+      </c>
+      <c r="B265">
+        <v>4</v>
+      </c>
+      <c r="C265" t="s">
+        <v>56</v>
+      </c>
+      <c r="D265">
+        <v>428</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="F265" t="s">
+        <v>14</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
+      </c>
+      <c r="H265">
+        <v>81</v>
+      </c>
+      <c r="I265">
+        <v>1</v>
+      </c>
+      <c r="J265" t="s">
+        <v>15</v>
+      </c>
+      <c r="K265" t="s">
+        <v>15</v>
+      </c>
+      <c r="L265" t="s">
+        <v>15</v>
+      </c>
+      <c r="M265">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>2026</v>
+      </c>
+      <c r="B266">
+        <v>4</v>
+      </c>
+      <c r="C266" t="s">
+        <v>56</v>
+      </c>
+      <c r="D266">
+        <v>428</v>
+      </c>
+      <c r="E266">
+        <v>1</v>
+      </c>
+      <c r="F266" t="s">
+        <v>14</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
+      </c>
+      <c r="H266">
+        <v>73</v>
+      </c>
+      <c r="I266">
+        <v>2</v>
+      </c>
+      <c r="J266" t="s">
+        <v>15</v>
+      </c>
+      <c r="K266" t="s">
+        <v>15</v>
+      </c>
+      <c r="L266" t="s">
+        <v>15</v>
+      </c>
+      <c r="M266">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>2026</v>
+      </c>
+      <c r="B267">
+        <v>4</v>
+      </c>
+      <c r="C267" t="s">
+        <v>56</v>
+      </c>
+      <c r="D267">
+        <v>428</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+      <c r="F267" t="s">
+        <v>14</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>76</v>
+      </c>
+      <c r="I267">
+        <v>3</v>
+      </c>
+      <c r="J267" t="s">
+        <v>15</v>
+      </c>
+      <c r="K267" t="s">
+        <v>15</v>
+      </c>
+      <c r="L267" t="s">
+        <v>15</v>
+      </c>
+      <c r="M267">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>2026</v>
+      </c>
+      <c r="B268">
+        <v>4</v>
+      </c>
+      <c r="C268" t="s">
+        <v>56</v>
+      </c>
+      <c r="D268">
+        <v>428</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+      <c r="F268" t="s">
+        <v>14</v>
+      </c>
+      <c r="G268">
+        <v>0</v>
+      </c>
+      <c r="H268">
+        <v>74</v>
+      </c>
+      <c r="I268">
+        <v>1</v>
+      </c>
+      <c r="J268" t="s">
+        <v>15</v>
+      </c>
+      <c r="K268" t="s">
+        <v>15</v>
+      </c>
+      <c r="L268" t="s">
+        <v>15</v>
+      </c>
+      <c r="M268">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>2026</v>
+      </c>
+      <c r="B269">
+        <v>4</v>
+      </c>
+      <c r="C269" t="s">
+        <v>56</v>
+      </c>
+      <c r="D269">
+        <v>428</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="F269" t="s">
+        <v>14</v>
+      </c>
+      <c r="G269">
+        <v>0</v>
+      </c>
+      <c r="H269">
+        <v>80</v>
+      </c>
+      <c r="I269">
+        <v>2</v>
+      </c>
+      <c r="J269" t="s">
+        <v>15</v>
+      </c>
+      <c r="K269" t="s">
+        <v>15</v>
+      </c>
+      <c r="L269" t="s">
+        <v>15</v>
+      </c>
+      <c r="M269">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>2026</v>
+      </c>
+      <c r="B270">
+        <v>4</v>
+      </c>
+      <c r="C270" t="s">
+        <v>56</v>
+      </c>
+      <c r="D270">
+        <v>428</v>
+      </c>
+      <c r="E270">
+        <v>1</v>
+      </c>
+      <c r="F270" t="s">
+        <v>14</v>
+      </c>
+      <c r="G270">
+        <v>0</v>
+      </c>
+      <c r="H270">
+        <v>88</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270" t="s">
+        <v>15</v>
+      </c>
+      <c r="K270" t="s">
+        <v>15</v>
+      </c>
+      <c r="L270" t="s">
+        <v>15</v>
+      </c>
+      <c r="M270">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>2026</v>
+      </c>
+      <c r="B271">
+        <v>4</v>
+      </c>
+      <c r="C271" t="s">
+        <v>56</v>
+      </c>
+      <c r="D271">
+        <v>428</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+      <c r="F271" t="s">
+        <v>14</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <v>75</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271" t="s">
+        <v>15</v>
+      </c>
+      <c r="K271" t="s">
+        <v>15</v>
+      </c>
+      <c r="L271" t="s">
+        <v>15</v>
+      </c>
+      <c r="M271">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>2026</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>56</v>
+      </c>
+      <c r="D272">
+        <v>428</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="F272" t="s">
+        <v>14</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>86</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272" t="s">
+        <v>15</v>
+      </c>
+      <c r="K272" t="s">
+        <v>15</v>
+      </c>
+      <c r="L272" t="s">
+        <v>15</v>
+      </c>
+      <c r="M272">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>2026</v>
+      </c>
+      <c r="B273">
+        <v>4</v>
+      </c>
+      <c r="C273" t="s">
+        <v>56</v>
+      </c>
+      <c r="D273">
+        <v>428</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="F273" t="s">
+        <v>14</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>85</v>
+      </c>
+      <c r="I273">
+        <v>3</v>
+      </c>
+      <c r="J273" t="s">
+        <v>15</v>
+      </c>
+      <c r="K273" t="s">
+        <v>15</v>
+      </c>
+      <c r="L273" t="s">
+        <v>15</v>
+      </c>
+      <c r="M273">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>2026</v>
+      </c>
+      <c r="B274">
+        <v>4</v>
+      </c>
+      <c r="C274" t="s">
+        <v>56</v>
+      </c>
+      <c r="D274">
+        <v>428</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
+      <c r="F274" t="s">
+        <v>14</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274">
+        <v>72</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+      <c r="J274" t="s">
+        <v>15</v>
+      </c>
+      <c r="K274" t="s">
+        <v>15</v>
+      </c>
+      <c r="L274" t="s">
+        <v>15</v>
+      </c>
+      <c r="M274">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>2026</v>
+      </c>
+      <c r="B275">
+        <v>4</v>
+      </c>
+      <c r="C275" t="s">
+        <v>56</v>
+      </c>
+      <c r="D275">
+        <v>428</v>
+      </c>
+      <c r="E275">
+        <v>1</v>
+      </c>
+      <c r="F275" t="s">
+        <v>14</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>84</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275" t="s">
+        <v>15</v>
+      </c>
+      <c r="K275" t="s">
+        <v>15</v>
+      </c>
+      <c r="L275" t="s">
+        <v>15</v>
+      </c>
+      <c r="M275">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>2026</v>
+      </c>
+      <c r="B276">
+        <v>4</v>
+      </c>
+      <c r="C276" t="s">
+        <v>56</v>
+      </c>
+      <c r="D276">
+        <v>428</v>
+      </c>
+      <c r="E276">
+        <v>1</v>
+      </c>
+      <c r="F276" t="s">
+        <v>14</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>90</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+      <c r="J276" t="s">
+        <v>15</v>
+      </c>
+      <c r="K276" t="s">
+        <v>15</v>
+      </c>
+      <c r="L276" t="s">
+        <v>15</v>
+      </c>
+      <c r="M276">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>2026</v>
+      </c>
+      <c r="B277">
+        <v>4</v>
+      </c>
+      <c r="C277" t="s">
+        <v>56</v>
+      </c>
+      <c r="D277">
+        <v>428</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="F277" t="s">
+        <v>14</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>89</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277" t="s">
+        <v>15</v>
+      </c>
+      <c r="K277" t="s">
+        <v>15</v>
+      </c>
+      <c r="L277" t="s">
+        <v>15</v>
+      </c>
+      <c r="M277">
+        <v>5387.4624999999996</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>2026</v>
+      </c>
+      <c r="B278">
+        <v>4</v>
+      </c>
+      <c r="C278" t="s">
+        <v>56</v>
+      </c>
+      <c r="D278">
+        <v>430</v>
+      </c>
+      <c r="E278">
+        <v>2</v>
+      </c>
+      <c r="F278" t="s">
+        <v>14</v>
+      </c>
+      <c r="G278">
+        <v>8</v>
+      </c>
+      <c r="H278">
+        <v>30</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278" t="s">
+        <v>15</v>
+      </c>
+      <c r="K278" t="s">
+        <v>15</v>
+      </c>
+      <c r="L278">
+        <v>823.93996979999997</v>
+      </c>
+      <c r="M278" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>2026</v>
+      </c>
+      <c r="B279">
+        <v>4</v>
+      </c>
+      <c r="C279" t="s">
+        <v>56</v>
+      </c>
+      <c r="D279">
+        <v>430</v>
+      </c>
+      <c r="E279">
+        <v>2</v>
+      </c>
+      <c r="F279" t="s">
+        <v>14</v>
+      </c>
+      <c r="G279">
+        <v>8</v>
+      </c>
+      <c r="H279">
+        <v>28</v>
+      </c>
+      <c r="I279">
+        <v>1</v>
+      </c>
+      <c r="J279" t="s">
+        <v>15</v>
+      </c>
+      <c r="K279" t="s">
+        <v>15</v>
+      </c>
+      <c r="L279">
+        <v>823.93996979999997</v>
+      </c>
+      <c r="M279" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>2026</v>
+      </c>
+      <c r="B280">
+        <v>4</v>
+      </c>
+      <c r="C280" t="s">
+        <v>56</v>
+      </c>
+      <c r="D280">
+        <v>430</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+      <c r="F280" t="s">
+        <v>14</v>
+      </c>
+      <c r="G280">
+        <v>8</v>
+      </c>
+      <c r="H280">
+        <v>25</v>
+      </c>
+      <c r="I280">
+        <v>1</v>
+      </c>
+      <c r="J280" t="s">
+        <v>15</v>
+      </c>
+      <c r="K280" t="s">
+        <v>15</v>
+      </c>
+      <c r="L280" t="s">
+        <v>15</v>
+      </c>
+      <c r="M280">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>2026</v>
+      </c>
+      <c r="B281">
+        <v>4</v>
+      </c>
+      <c r="C281" t="s">
+        <v>56</v>
+      </c>
+      <c r="D281">
+        <v>430</v>
+      </c>
+      <c r="E281">
+        <v>1</v>
+      </c>
+      <c r="F281" t="s">
+        <v>14</v>
+      </c>
+      <c r="G281">
+        <v>8</v>
+      </c>
+      <c r="H281">
+        <v>29</v>
+      </c>
+      <c r="I281">
+        <v>2</v>
+      </c>
+      <c r="J281" t="s">
+        <v>15</v>
+      </c>
+      <c r="K281" t="s">
+        <v>15</v>
+      </c>
+      <c r="L281" t="s">
+        <v>15</v>
+      </c>
+      <c r="M281">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>2026</v>
+      </c>
+      <c r="B282">
+        <v>4</v>
+      </c>
+      <c r="C282" t="s">
+        <v>56</v>
+      </c>
+      <c r="D282">
+        <v>430</v>
+      </c>
+      <c r="E282">
+        <v>1</v>
+      </c>
+      <c r="F282" t="s">
+        <v>14</v>
+      </c>
+      <c r="G282">
+        <v>8</v>
+      </c>
+      <c r="H282">
+        <v>33</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282" t="s">
+        <v>15</v>
+      </c>
+      <c r="K282" t="s">
+        <v>15</v>
+      </c>
+      <c r="L282" t="s">
+        <v>15</v>
+      </c>
+      <c r="M282">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>2026</v>
+      </c>
+      <c r="B283">
+        <v>4</v>
+      </c>
+      <c r="C283" t="s">
+        <v>56</v>
+      </c>
+      <c r="D283">
+        <v>430</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
+      <c r="F283" t="s">
+        <v>14</v>
+      </c>
+      <c r="G283">
+        <v>8</v>
+      </c>
+      <c r="H283">
+        <v>30</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283" t="s">
+        <v>15</v>
+      </c>
+      <c r="K283" t="s">
+        <v>15</v>
+      </c>
+      <c r="L283" t="s">
+        <v>15</v>
+      </c>
+      <c r="M283">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>2026</v>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
+      <c r="C284" t="s">
+        <v>56</v>
+      </c>
+      <c r="D284">
+        <v>430</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284" t="s">
+        <v>14</v>
+      </c>
+      <c r="G284">
+        <v>8</v>
+      </c>
+      <c r="H284">
+        <v>23</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+      <c r="J284" t="s">
+        <v>15</v>
+      </c>
+      <c r="K284" t="s">
+        <v>15</v>
+      </c>
+      <c r="L284" t="s">
+        <v>15</v>
+      </c>
+      <c r="M284">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>2026</v>
+      </c>
+      <c r="B285">
+        <v>4</v>
+      </c>
+      <c r="C285" t="s">
+        <v>56</v>
+      </c>
+      <c r="D285">
+        <v>430</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285" t="s">
+        <v>14</v>
+      </c>
+      <c r="G285">
+        <v>8</v>
+      </c>
+      <c r="H285">
+        <v>31</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+      <c r="J285" t="s">
+        <v>15</v>
+      </c>
+      <c r="K285" t="s">
+        <v>15</v>
+      </c>
+      <c r="L285" t="s">
+        <v>15</v>
+      </c>
+      <c r="M285">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>2026</v>
+      </c>
+      <c r="B286">
+        <v>4</v>
+      </c>
+      <c r="C286" t="s">
+        <v>56</v>
+      </c>
+      <c r="D286">
+        <v>430</v>
+      </c>
+      <c r="E286">
+        <v>1</v>
+      </c>
+      <c r="F286" t="s">
+        <v>14</v>
+      </c>
+      <c r="G286">
+        <v>8</v>
+      </c>
+      <c r="H286">
+        <v>27</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286" t="s">
+        <v>15</v>
+      </c>
+      <c r="K286" t="s">
+        <v>15</v>
+      </c>
+      <c r="L286" t="s">
+        <v>15</v>
+      </c>
+      <c r="M286">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>2026</v>
+      </c>
+      <c r="B287">
+        <v>4</v>
+      </c>
+      <c r="C287" t="s">
+        <v>56</v>
+      </c>
+      <c r="D287">
+        <v>430</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+      <c r="F287" t="s">
+        <v>14</v>
+      </c>
+      <c r="G287">
+        <v>8</v>
+      </c>
+      <c r="H287">
+        <v>36</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287" t="s">
+        <v>15</v>
+      </c>
+      <c r="K287" t="s">
+        <v>15</v>
+      </c>
+      <c r="L287" t="s">
+        <v>15</v>
+      </c>
+      <c r="M287">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>2026</v>
+      </c>
+      <c r="B288">
+        <v>4</v>
+      </c>
+      <c r="C288" t="s">
+        <v>56</v>
+      </c>
+      <c r="D288">
+        <v>430</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+      <c r="F288" t="s">
+        <v>14</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>83</v>
+      </c>
+      <c r="I288">
+        <v>2</v>
+      </c>
+      <c r="J288" t="s">
+        <v>15</v>
+      </c>
+      <c r="K288" t="s">
+        <v>15</v>
+      </c>
+      <c r="L288" t="s">
+        <v>15</v>
+      </c>
+      <c r="M288">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>2026</v>
+      </c>
+      <c r="B289">
+        <v>4</v>
+      </c>
+      <c r="C289" t="s">
+        <v>56</v>
+      </c>
+      <c r="D289">
+        <v>430</v>
+      </c>
+      <c r="E289">
+        <v>1</v>
+      </c>
+      <c r="F289" t="s">
+        <v>14</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>69</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289" t="s">
+        <v>15</v>
+      </c>
+      <c r="K289" t="s">
+        <v>15</v>
+      </c>
+      <c r="L289" t="s">
+        <v>15</v>
+      </c>
+      <c r="M289">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>2026</v>
+      </c>
+      <c r="B290">
+        <v>4</v>
+      </c>
+      <c r="C290" t="s">
+        <v>56</v>
+      </c>
+      <c r="D290">
+        <v>430</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>14</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290">
+        <v>79</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290" t="s">
+        <v>15</v>
+      </c>
+      <c r="K290" t="s">
+        <v>15</v>
+      </c>
+      <c r="L290" t="s">
+        <v>15</v>
+      </c>
+      <c r="M290">
+        <v>6756.5375000000004</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>2026</v>
+      </c>
+      <c r="B291">
+        <v>4</v>
+      </c>
+      <c r="C291" t="s">
+        <v>56</v>
+      </c>
+      <c r="D291">
+        <v>432</v>
+      </c>
+      <c r="E291">
+        <v>1</v>
+      </c>
+      <c r="F291" t="s">
+        <v>14</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>88</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291" t="s">
+        <v>15</v>
+      </c>
+      <c r="K291" t="s">
+        <v>15</v>
+      </c>
+      <c r="L291" t="s">
+        <v>15</v>
+      </c>
+      <c r="M291">
+        <v>5762.9375</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>2026</v>
+      </c>
+      <c r="B292">
+        <v>4</v>
+      </c>
+      <c r="C292" t="s">
+        <v>56</v>
+      </c>
+      <c r="D292">
+        <v>433</v>
+      </c>
+      <c r="E292">
+        <v>1</v>
+      </c>
+      <c r="F292" t="s">
+        <v>14</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>83</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292" t="s">
+        <v>15</v>
+      </c>
+      <c r="K292" t="s">
+        <v>15</v>
+      </c>
+      <c r="L292" t="s">
+        <v>15</v>
+      </c>
+      <c r="M292">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>2026</v>
+      </c>
+      <c r="B293">
+        <v>4</v>
+      </c>
+      <c r="C293" t="s">
+        <v>56</v>
+      </c>
+      <c r="D293">
+        <v>433</v>
+      </c>
+      <c r="E293">
+        <v>1</v>
+      </c>
+      <c r="F293" t="s">
+        <v>14</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>79</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293" t="s">
+        <v>15</v>
+      </c>
+      <c r="K293" t="s">
+        <v>15</v>
+      </c>
+      <c r="L293" t="s">
+        <v>15</v>
+      </c>
+      <c r="M293">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>2026</v>
+      </c>
+      <c r="B294">
+        <v>4</v>
+      </c>
+      <c r="C294" t="s">
+        <v>56</v>
+      </c>
+      <c r="D294">
+        <v>433</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+      <c r="F294" t="s">
+        <v>14</v>
+      </c>
+      <c r="G294">
+        <v>8</v>
+      </c>
+      <c r="H294">
+        <v>23</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294" t="s">
+        <v>15</v>
+      </c>
+      <c r="K294" t="s">
+        <v>15</v>
+      </c>
+      <c r="L294" t="s">
+        <v>15</v>
+      </c>
+      <c r="M294">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>2026</v>
+      </c>
+      <c r="B295">
+        <v>4</v>
+      </c>
+      <c r="C295" t="s">
+        <v>56</v>
+      </c>
+      <c r="D295">
+        <v>433</v>
+      </c>
+      <c r="E295">
+        <v>1</v>
+      </c>
+      <c r="F295" t="s">
+        <v>14</v>
+      </c>
+      <c r="G295">
+        <v>8</v>
+      </c>
+      <c r="H295">
+        <v>33</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295" t="s">
+        <v>15</v>
+      </c>
+      <c r="K295" t="s">
+        <v>15</v>
+      </c>
+      <c r="L295" t="s">
+        <v>15</v>
+      </c>
+      <c r="M295">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>2026</v>
+      </c>
+      <c r="B296">
+        <v>4</v>
+      </c>
+      <c r="C296" t="s">
+        <v>56</v>
+      </c>
+      <c r="D296">
+        <v>433</v>
+      </c>
+      <c r="E296">
+        <v>1</v>
+      </c>
+      <c r="F296" t="s">
+        <v>14</v>
+      </c>
+      <c r="G296">
+        <v>8</v>
+      </c>
+      <c r="H296">
+        <v>32</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296" t="s">
+        <v>15</v>
+      </c>
+      <c r="K296" t="s">
+        <v>15</v>
+      </c>
+      <c r="L296" t="s">
+        <v>15</v>
+      </c>
+      <c r="M296">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>2026</v>
+      </c>
+      <c r="B297">
+        <v>4</v>
+      </c>
+      <c r="C297" t="s">
+        <v>56</v>
+      </c>
+      <c r="D297">
+        <v>433</v>
+      </c>
+      <c r="E297">
+        <v>1</v>
+      </c>
+      <c r="F297" t="s">
+        <v>14</v>
+      </c>
+      <c r="G297">
+        <v>8</v>
+      </c>
+      <c r="H297">
+        <v>29</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297" t="s">
+        <v>15</v>
+      </c>
+      <c r="K297" t="s">
+        <v>15</v>
+      </c>
+      <c r="L297" t="s">
+        <v>15</v>
+      </c>
+      <c r="M297">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>2026</v>
+      </c>
+      <c r="B298">
+        <v>4</v>
+      </c>
+      <c r="C298" t="s">
+        <v>56</v>
+      </c>
+      <c r="D298">
+        <v>433</v>
+      </c>
+      <c r="E298">
+        <v>1</v>
+      </c>
+      <c r="F298" t="s">
+        <v>14</v>
+      </c>
+      <c r="G298">
+        <v>8</v>
+      </c>
+      <c r="H298">
+        <v>20</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298" t="s">
+        <v>15</v>
+      </c>
+      <c r="K298" t="s">
+        <v>15</v>
+      </c>
+      <c r="L298" t="s">
+        <v>15</v>
+      </c>
+      <c r="M298">
+        <v>6280.15</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>2026</v>
+      </c>
+      <c r="B299">
+        <v>4</v>
+      </c>
+      <c r="C299" t="s">
+        <v>56</v>
+      </c>
+      <c r="D299">
+        <v>433</v>
+      </c>
+      <c r="E299">
+        <v>2</v>
+      </c>
+      <c r="F299" t="s">
+        <v>14</v>
+      </c>
+      <c r="G299">
+        <v>8</v>
+      </c>
+      <c r="H299">
+        <v>31</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299" t="s">
+        <v>15</v>
+      </c>
+      <c r="K299" t="s">
+        <v>15</v>
+      </c>
+      <c r="L299">
+        <v>1077.4600109999999</v>
+      </c>
+      <c r="M299" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>2026</v>
+      </c>
+      <c r="B300">
+        <v>4</v>
+      </c>
+      <c r="C300" t="s">
+        <v>56</v>
+      </c>
+      <c r="D300">
+        <v>433</v>
+      </c>
+      <c r="E300">
+        <v>2</v>
+      </c>
+      <c r="F300" t="s">
+        <v>14</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>76</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300" t="s">
+        <v>15</v>
+      </c>
+      <c r="K300" t="s">
+        <v>15</v>
+      </c>
+      <c r="L300">
+        <v>1077.4600109999999</v>
+      </c>
+      <c r="M300" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>2026</v>
+      </c>
+      <c r="B301">
+        <v>4</v>
+      </c>
+      <c r="C301" t="s">
+        <v>56</v>
+      </c>
+      <c r="D301">
+        <v>534</v>
+      </c>
+      <c r="E301">
+        <v>2</v>
+      </c>
+      <c r="F301" t="s">
+        <v>14</v>
+      </c>
+      <c r="G301">
+        <v>8</v>
+      </c>
+      <c r="H301">
+        <v>27</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301" t="s">
+        <v>15</v>
+      </c>
+      <c r="K301" t="s">
+        <v>15</v>
+      </c>
+      <c r="L301">
+        <v>1077.4600109999999</v>
+      </c>
+      <c r="M301" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>2026</v>
+      </c>
+      <c r="B302">
+        <v>4</v>
+      </c>
+      <c r="C302" t="s">
+        <v>56</v>
+      </c>
+      <c r="D302">
+        <v>534</v>
+      </c>
+      <c r="E302">
+        <v>1</v>
+      </c>
+      <c r="F302" t="s">
+        <v>14</v>
+      </c>
+      <c r="G302">
+        <v>8</v>
+      </c>
+      <c r="H302">
+        <v>26</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+      <c r="J302" t="s">
+        <v>15</v>
+      </c>
+      <c r="K302" t="s">
+        <v>15</v>
+      </c>
+      <c r="L302" t="s">
+        <v>15</v>
+      </c>
+      <c r="M302">
+        <v>6927.8874999999998</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>2026</v>
+      </c>
+      <c r="B303">
+        <v>4</v>
+      </c>
+      <c r="C303" t="s">
+        <v>56</v>
+      </c>
+      <c r="D303">
+        <v>535</v>
+      </c>
+      <c r="E303">
+        <v>1</v>
+      </c>
+      <c r="F303" t="s">
+        <v>14</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>83</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303" t="s">
+        <v>15</v>
+      </c>
+      <c r="K303" t="s">
+        <v>15</v>
+      </c>
+      <c r="L303" t="s">
+        <v>15</v>
+      </c>
+      <c r="M303">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>2026</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304" t="s">
+        <v>56</v>
+      </c>
+      <c r="D304">
+        <v>535</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+      <c r="F304" t="s">
+        <v>14</v>
+      </c>
+      <c r="G304">
+        <v>8</v>
+      </c>
+      <c r="H304">
+        <v>21</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304" t="s">
+        <v>15</v>
+      </c>
+      <c r="K304" t="s">
+        <v>15</v>
+      </c>
+      <c r="L304" t="s">
+        <v>15</v>
+      </c>
+      <c r="M304">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>2026</v>
+      </c>
+      <c r="B305">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>56</v>
+      </c>
+      <c r="D305">
+        <v>535</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
+      <c r="F305" t="s">
+        <v>14</v>
+      </c>
+      <c r="G305">
+        <v>8</v>
+      </c>
+      <c r="H305">
+        <v>22</v>
+      </c>
+      <c r="I305">
+        <v>3</v>
+      </c>
+      <c r="J305" t="s">
+        <v>15</v>
+      </c>
+      <c r="K305" t="s">
+        <v>15</v>
+      </c>
+      <c r="L305" t="s">
+        <v>15</v>
+      </c>
+      <c r="M305">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>2026</v>
+      </c>
+      <c r="B306">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>56</v>
+      </c>
+      <c r="D306">
+        <v>535</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+      <c r="F306" t="s">
+        <v>14</v>
+      </c>
+      <c r="G306">
+        <v>8</v>
+      </c>
+      <c r="H306">
+        <v>23</v>
+      </c>
+      <c r="I306">
+        <v>3</v>
+      </c>
+      <c r="J306" t="s">
+        <v>15</v>
+      </c>
+      <c r="K306" t="s">
+        <v>15</v>
+      </c>
+      <c r="L306" t="s">
+        <v>15</v>
+      </c>
+      <c r="M306">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>2026</v>
+      </c>
+      <c r="B307">
+        <v>4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>56</v>
+      </c>
+      <c r="D307">
+        <v>535</v>
+      </c>
+      <c r="E307">
+        <v>1</v>
+      </c>
+      <c r="F307" t="s">
+        <v>14</v>
+      </c>
+      <c r="G307">
+        <v>8</v>
+      </c>
+      <c r="H307">
+        <v>25</v>
+      </c>
+      <c r="I307">
+        <v>1</v>
+      </c>
+      <c r="J307" t="s">
+        <v>15</v>
+      </c>
+      <c r="K307" t="s">
+        <v>15</v>
+      </c>
+      <c r="L307" t="s">
+        <v>15</v>
+      </c>
+      <c r="M307">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>2026</v>
+      </c>
+      <c r="B308">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>56</v>
+      </c>
+      <c r="D308">
+        <v>535</v>
+      </c>
+      <c r="E308">
+        <v>1</v>
+      </c>
+      <c r="F308" t="s">
+        <v>14</v>
+      </c>
+      <c r="G308">
+        <v>8</v>
+      </c>
+      <c r="H308">
+        <v>24</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+      <c r="J308" t="s">
+        <v>15</v>
+      </c>
+      <c r="K308" t="s">
+        <v>15</v>
+      </c>
+      <c r="L308" t="s">
+        <v>15</v>
+      </c>
+      <c r="M308">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>2026</v>
+      </c>
+      <c r="B309">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>56</v>
+      </c>
+      <c r="D309">
+        <v>535</v>
+      </c>
+      <c r="E309">
+        <v>1</v>
+      </c>
+      <c r="F309" t="s">
+        <v>14</v>
+      </c>
+      <c r="G309">
+        <v>8</v>
+      </c>
+      <c r="H309">
+        <v>20</v>
+      </c>
+      <c r="I309">
+        <v>1</v>
+      </c>
+      <c r="J309" t="s">
+        <v>15</v>
+      </c>
+      <c r="K309" t="s">
+        <v>15</v>
+      </c>
+      <c r="L309" t="s">
+        <v>15</v>
+      </c>
+      <c r="M309">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>2026</v>
+      </c>
+      <c r="B310">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>56</v>
+      </c>
+      <c r="D310">
+        <v>535</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="F310" t="s">
+        <v>14</v>
+      </c>
+      <c r="G310">
+        <v>8</v>
+      </c>
+      <c r="H310">
+        <v>31</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+      <c r="J310" t="s">
+        <v>15</v>
+      </c>
+      <c r="K310" t="s">
+        <v>15</v>
+      </c>
+      <c r="L310" t="s">
+        <v>15</v>
+      </c>
+      <c r="M310">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>2026</v>
+      </c>
+      <c r="B311">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>56</v>
+      </c>
+      <c r="D311">
+        <v>535</v>
+      </c>
+      <c r="E311">
+        <v>1</v>
+      </c>
+      <c r="F311" t="s">
+        <v>14</v>
+      </c>
+      <c r="G311">
+        <v>8</v>
+      </c>
+      <c r="H311">
+        <v>26</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311" t="s">
+        <v>15</v>
+      </c>
+      <c r="K311" t="s">
+        <v>15</v>
+      </c>
+      <c r="L311" t="s">
+        <v>15</v>
+      </c>
+      <c r="M311">
+        <v>7386.45</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>2026</v>
+      </c>
+      <c r="B312">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>57</v>
+      </c>
+      <c r="D312">
+        <v>736</v>
+      </c>
+      <c r="E312">
+        <v>1</v>
+      </c>
+      <c r="F312" t="s">
+        <v>14</v>
+      </c>
+      <c r="G312">
+        <v>8</v>
+      </c>
+      <c r="H312">
+        <v>21</v>
+      </c>
+      <c r="I312">
+        <v>8</v>
+      </c>
+      <c r="J312" t="s">
+        <v>15</v>
+      </c>
+      <c r="K312" t="s">
+        <v>15</v>
+      </c>
+      <c r="L312" t="s">
+        <v>15</v>
+      </c>
+      <c r="M312">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>2026</v>
+      </c>
+      <c r="B313">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>57</v>
+      </c>
+      <c r="D313">
+        <v>736</v>
+      </c>
+      <c r="E313">
+        <v>1</v>
+      </c>
+      <c r="F313" t="s">
+        <v>14</v>
+      </c>
+      <c r="G313">
+        <v>8</v>
+      </c>
+      <c r="H313">
+        <v>24</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+      <c r="J313" t="s">
+        <v>15</v>
+      </c>
+      <c r="K313" t="s">
+        <v>15</v>
+      </c>
+      <c r="L313" t="s">
+        <v>15</v>
+      </c>
+      <c r="M313">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>2026</v>
+      </c>
+      <c r="B314">
+        <v>4</v>
+      </c>
+      <c r="C314" t="s">
+        <v>57</v>
+      </c>
+      <c r="D314">
+        <v>736</v>
+      </c>
+      <c r="E314">
+        <v>1</v>
+      </c>
+      <c r="F314" t="s">
+        <v>14</v>
+      </c>
+      <c r="G314">
+        <v>8</v>
+      </c>
+      <c r="H314">
+        <v>22</v>
+      </c>
+      <c r="I314">
+        <v>8</v>
+      </c>
+      <c r="J314" t="s">
+        <v>15</v>
+      </c>
+      <c r="K314" t="s">
+        <v>15</v>
+      </c>
+      <c r="L314" t="s">
+        <v>15</v>
+      </c>
+      <c r="M314">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>2026</v>
+      </c>
+      <c r="B315">
+        <v>4</v>
+      </c>
+      <c r="C315" t="s">
+        <v>57</v>
+      </c>
+      <c r="D315">
+        <v>736</v>
+      </c>
+      <c r="E315">
+        <v>1</v>
+      </c>
+      <c r="F315" t="s">
+        <v>14</v>
+      </c>
+      <c r="G315">
+        <v>8</v>
+      </c>
+      <c r="H315">
+        <v>20</v>
+      </c>
+      <c r="I315">
+        <v>6</v>
+      </c>
+      <c r="J315" t="s">
+        <v>15</v>
+      </c>
+      <c r="K315" t="s">
+        <v>15</v>
+      </c>
+      <c r="L315" t="s">
+        <v>15</v>
+      </c>
+      <c r="M315">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>2026</v>
+      </c>
+      <c r="B316">
+        <v>4</v>
+      </c>
+      <c r="C316" t="s">
+        <v>57</v>
+      </c>
+      <c r="D316">
+        <v>736</v>
+      </c>
+      <c r="E316">
+        <v>1</v>
+      </c>
+      <c r="F316" t="s">
+        <v>14</v>
+      </c>
+      <c r="G316">
+        <v>8</v>
+      </c>
+      <c r="H316">
+        <v>23</v>
+      </c>
+      <c r="I316">
+        <v>5</v>
+      </c>
+      <c r="J316" t="s">
+        <v>15</v>
+      </c>
+      <c r="K316" t="s">
+        <v>15</v>
+      </c>
+      <c r="L316" t="s">
+        <v>15</v>
+      </c>
+      <c r="M316">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>2026</v>
+      </c>
+      <c r="B317">
+        <v>4</v>
+      </c>
+      <c r="C317" t="s">
+        <v>57</v>
+      </c>
+      <c r="D317">
+        <v>736</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+      <c r="F317" t="s">
+        <v>14</v>
+      </c>
+      <c r="G317">
+        <v>8</v>
+      </c>
+      <c r="H317">
+        <v>27</v>
+      </c>
+      <c r="I317">
+        <v>1</v>
+      </c>
+      <c r="J317" t="s">
+        <v>15</v>
+      </c>
+      <c r="K317" t="s">
+        <v>15</v>
+      </c>
+      <c r="L317" t="s">
+        <v>15</v>
+      </c>
+      <c r="M317">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>2026</v>
+      </c>
+      <c r="B318">
+        <v>4</v>
+      </c>
+      <c r="C318" t="s">
+        <v>57</v>
+      </c>
+      <c r="D318">
+        <v>736</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="F318" t="s">
+        <v>14</v>
+      </c>
+      <c r="G318">
+        <v>8</v>
+      </c>
+      <c r="H318">
+        <v>28</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+      <c r="J318" t="s">
+        <v>15</v>
+      </c>
+      <c r="K318" t="s">
+        <v>15</v>
+      </c>
+      <c r="L318" t="s">
+        <v>15</v>
+      </c>
+      <c r="M318">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>2026</v>
+      </c>
+      <c r="B319">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>57</v>
+      </c>
+      <c r="D319">
+        <v>736</v>
+      </c>
+      <c r="E319">
+        <v>1</v>
+      </c>
+      <c r="F319" t="s">
+        <v>14</v>
+      </c>
+      <c r="H319" t="s">
+        <v>15</v>
+      </c>
+      <c r="I319" t="s">
+        <v>15</v>
+      </c>
+      <c r="J319">
+        <v>2</v>
+      </c>
+      <c r="K319" t="s">
+        <v>15</v>
+      </c>
+      <c r="L319" t="s">
+        <v>15</v>
+      </c>
+      <c r="M319">
+        <v>7870.6</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>2026</v>
+      </c>
+      <c r="B320">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>57</v>
+      </c>
+      <c r="D320">
+        <v>750</v>
+      </c>
+      <c r="E320">
+        <v>1</v>
+      </c>
+      <c r="F320" t="s">
+        <v>14</v>
+      </c>
+      <c r="G320">
+        <v>8</v>
+      </c>
+      <c r="H320">
+        <v>23</v>
+      </c>
+      <c r="I320">
+        <v>2</v>
+      </c>
+      <c r="J320" t="s">
+        <v>15</v>
+      </c>
+      <c r="K320" t="s">
+        <v>15</v>
+      </c>
+      <c r="L320" t="s">
+        <v>15</v>
+      </c>
+      <c r="M320">
+        <v>7146.9624999999996</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>2026</v>
+      </c>
+      <c r="B321">
+        <v>4</v>
+      </c>
+      <c r="C321" t="s">
+        <v>57</v>
+      </c>
+      <c r="D321">
+        <v>750</v>
+      </c>
+      <c r="E321">
+        <v>1</v>
+      </c>
+      <c r="F321" t="s">
+        <v>14</v>
+      </c>
+      <c r="G321">
+        <v>8</v>
+      </c>
+      <c r="H321">
+        <v>22</v>
+      </c>
+      <c r="I321">
+        <v>4</v>
+      </c>
+      <c r="J321" t="s">
+        <v>15</v>
+      </c>
+      <c r="K321" t="s">
+        <v>15</v>
+      </c>
+      <c r="L321" t="s">
+        <v>15</v>
+      </c>
+      <c r="M321">
+        <v>7146.9624999999996</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>2026</v>
+      </c>
+      <c r="B322">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>57</v>
+      </c>
+      <c r="D322">
+        <v>750</v>
+      </c>
+      <c r="E322">
+        <v>1</v>
+      </c>
+      <c r="F322" t="s">
+        <v>14</v>
+      </c>
+      <c r="G322">
+        <v>8</v>
+      </c>
+      <c r="H322">
+        <v>21</v>
+      </c>
+      <c r="I322">
+        <v>1</v>
+      </c>
+      <c r="J322" t="s">
+        <v>15</v>
+      </c>
+      <c r="K322" t="s">
+        <v>15</v>
+      </c>
+      <c r="L322" t="s">
+        <v>15</v>
+      </c>
+      <c r="M322">
+        <v>7146.9624999999996</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>2026</v>
+      </c>
+      <c r="B323">
+        <v>5</v>
+      </c>
+      <c r="C323" t="s">
+        <v>58</v>
+      </c>
+      <c r="D323">
+        <v>216</v>
+      </c>
+      <c r="E323">
+        <v>2</v>
+      </c>
+      <c r="F323" t="s">
+        <v>14</v>
+      </c>
+      <c r="G323">
+        <v>8</v>
+      </c>
+      <c r="H323">
+        <v>39</v>
+      </c>
+      <c r="I323">
+        <v>1</v>
+      </c>
+      <c r="J323" t="s">
+        <v>15</v>
+      </c>
+      <c r="K323" t="s">
+        <v>15</v>
+      </c>
+      <c r="L323" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M323" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>2026</v>
+      </c>
+      <c r="B324">
+        <v>5</v>
+      </c>
+      <c r="C324" t="s">
+        <v>60</v>
+      </c>
+      <c r="D324">
+        <v>319</v>
+      </c>
+      <c r="E324">
+        <v>2</v>
+      </c>
+      <c r="F324" t="s">
+        <v>14</v>
+      </c>
+      <c r="G324">
+        <v>8</v>
+      </c>
+      <c r="H324">
+        <v>32</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+      <c r="J324" t="s">
+        <v>15</v>
+      </c>
+      <c r="K324" t="s">
+        <v>15</v>
+      </c>
+      <c r="L324" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M324" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>2026</v>
+      </c>
+      <c r="B325">
+        <v>5</v>
+      </c>
+      <c r="C325" t="s">
+        <v>60</v>
+      </c>
+      <c r="D325">
+        <v>325</v>
+      </c>
+      <c r="E325">
+        <v>1</v>
+      </c>
+      <c r="F325" t="s">
+        <v>14</v>
+      </c>
+      <c r="G325">
+        <v>0</v>
+      </c>
+      <c r="H325">
+        <v>52</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+      <c r="J325" t="s">
+        <v>15</v>
+      </c>
+      <c r="K325" t="s">
+        <v>15</v>
+      </c>
+      <c r="L325" t="s">
+        <v>15</v>
+      </c>
+      <c r="M325">
+        <v>5339.7375000000002</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>2026</v>
+      </c>
+      <c r="B326">
+        <v>5</v>
+      </c>
+      <c r="C326" t="s">
+        <v>60</v>
+      </c>
+      <c r="D326">
+        <v>325</v>
+      </c>
+      <c r="E326">
+        <v>1</v>
+      </c>
+      <c r="F326" t="s">
+        <v>14</v>
+      </c>
+      <c r="G326">
+        <v>0</v>
+      </c>
+      <c r="H326">
+        <v>49</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326" t="s">
+        <v>15</v>
+      </c>
+      <c r="K326" t="s">
+        <v>15</v>
+      </c>
+      <c r="L326" t="s">
+        <v>15</v>
+      </c>
+      <c r="M326">
+        <v>5339.7375000000002</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>2026</v>
+      </c>
+      <c r="B327">
+        <v>5</v>
+      </c>
+      <c r="C327" t="s">
+        <v>60</v>
+      </c>
+      <c r="D327">
+        <v>346</v>
+      </c>
+      <c r="E327">
+        <v>1</v>
+      </c>
+      <c r="F327" t="s">
+        <v>14</v>
+      </c>
+      <c r="G327">
+        <v>0</v>
+      </c>
+      <c r="H327">
+        <v>75</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327" t="s">
+        <v>15</v>
+      </c>
+      <c r="K327" t="s">
+        <v>15</v>
+      </c>
+      <c r="L327" t="s">
+        <v>15</v>
+      </c>
+      <c r="M327">
+        <v>4029.8874999999998</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>2026</v>
+      </c>
+      <c r="B328">
+        <v>5</v>
+      </c>
+      <c r="C328" t="s">
+        <v>60</v>
+      </c>
+      <c r="D328">
+        <v>346</v>
+      </c>
+      <c r="E328">
+        <v>1</v>
+      </c>
+      <c r="F328" t="s">
+        <v>14</v>
+      </c>
+      <c r="G328">
+        <v>0</v>
+      </c>
+      <c r="H328">
+        <v>52</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+      <c r="J328" t="s">
+        <v>15</v>
+      </c>
+      <c r="K328" t="s">
+        <v>15</v>
+      </c>
+      <c r="L328" t="s">
+        <v>15</v>
+      </c>
+      <c r="M328">
+        <v>4029.8874999999998</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>2026</v>
+      </c>
+      <c r="B329">
+        <v>5</v>
+      </c>
+      <c r="C329" t="s">
+        <v>60</v>
+      </c>
+      <c r="D329">
+        <v>346</v>
+      </c>
+      <c r="E329">
+        <v>1</v>
+      </c>
+      <c r="F329" t="s">
+        <v>14</v>
+      </c>
+      <c r="G329">
+        <v>8</v>
+      </c>
+      <c r="H329">
+        <v>34</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329" t="s">
+        <v>15</v>
+      </c>
+      <c r="K329" t="s">
+        <v>15</v>
+      </c>
+      <c r="L329" t="s">
+        <v>15</v>
+      </c>
+      <c r="M329">
+        <v>4029.8874999999998</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>2026</v>
+      </c>
+      <c r="B330">
+        <v>5</v>
+      </c>
+      <c r="C330" t="s">
+        <v>61</v>
+      </c>
+      <c r="D330">
+        <v>427</v>
+      </c>
+      <c r="E330">
+        <v>2</v>
+      </c>
+      <c r="F330" t="s">
+        <v>14</v>
+      </c>
+      <c r="G330">
+        <v>8</v>
+      </c>
+      <c r="H330">
+        <v>30</v>
+      </c>
+      <c r="I330">
+        <v>1</v>
+      </c>
+      <c r="J330" t="s">
+        <v>15</v>
+      </c>
+      <c r="K330" t="s">
+        <v>15</v>
+      </c>
+      <c r="L330" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M330" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>2026</v>
+      </c>
+      <c r="B331">
+        <v>5</v>
+      </c>
+      <c r="C331" t="s">
+        <v>61</v>
+      </c>
+      <c r="D331">
+        <v>427</v>
+      </c>
+      <c r="E331">
+        <v>1</v>
+      </c>
+      <c r="F331" t="s">
+        <v>14</v>
+      </c>
+      <c r="G331">
+        <v>8</v>
+      </c>
+      <c r="H331">
+        <v>34</v>
+      </c>
+      <c r="I331">
+        <v>2</v>
+      </c>
+      <c r="J331" t="s">
+        <v>15</v>
+      </c>
+      <c r="K331" t="s">
+        <v>15</v>
+      </c>
+      <c r="L331" t="s">
+        <v>15</v>
+      </c>
+      <c r="M331">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>2026</v>
+      </c>
+      <c r="B332">
+        <v>5</v>
+      </c>
+      <c r="C332" t="s">
+        <v>61</v>
+      </c>
+      <c r="D332">
+        <v>427</v>
+      </c>
+      <c r="E332">
+        <v>1</v>
+      </c>
+      <c r="F332" t="s">
+        <v>14</v>
+      </c>
+      <c r="G332">
+        <v>8</v>
+      </c>
+      <c r="H332">
+        <v>33</v>
+      </c>
+      <c r="I332">
+        <v>7</v>
+      </c>
+      <c r="J332" t="s">
+        <v>15</v>
+      </c>
+      <c r="K332" t="s">
+        <v>15</v>
+      </c>
+      <c r="L332" t="s">
+        <v>15</v>
+      </c>
+      <c r="M332">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>2026</v>
+      </c>
+      <c r="B333">
+        <v>5</v>
+      </c>
+      <c r="C333" t="s">
+        <v>61</v>
+      </c>
+      <c r="D333">
+        <v>427</v>
+      </c>
+      <c r="E333">
+        <v>1</v>
+      </c>
+      <c r="F333" t="s">
+        <v>14</v>
+      </c>
+      <c r="G333">
+        <v>8</v>
+      </c>
+      <c r="H333">
+        <v>39</v>
+      </c>
+      <c r="I333">
+        <v>2</v>
+      </c>
+      <c r="J333" t="s">
+        <v>15</v>
+      </c>
+      <c r="K333" t="s">
+        <v>15</v>
+      </c>
+      <c r="L333" t="s">
+        <v>15</v>
+      </c>
+      <c r="M333">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>2026</v>
+      </c>
+      <c r="B334">
+        <v>5</v>
+      </c>
+      <c r="C334" t="s">
+        <v>61</v>
+      </c>
+      <c r="D334">
+        <v>427</v>
+      </c>
+      <c r="E334">
+        <v>1</v>
+      </c>
+      <c r="F334" t="s">
+        <v>14</v>
+      </c>
+      <c r="G334">
+        <v>0</v>
+      </c>
+      <c r="H334">
+        <v>40</v>
+      </c>
+      <c r="I334">
+        <v>2</v>
+      </c>
+      <c r="J334" t="s">
+        <v>15</v>
+      </c>
+      <c r="K334" t="s">
+        <v>15</v>
+      </c>
+      <c r="L334" t="s">
+        <v>15</v>
+      </c>
+      <c r="M334">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <v>2026</v>
+      </c>
+      <c r="B335">
+        <v>5</v>
+      </c>
+      <c r="C335" t="s">
+        <v>61</v>
+      </c>
+      <c r="D335">
+        <v>427</v>
+      </c>
+      <c r="E335">
+        <v>1</v>
+      </c>
+      <c r="F335" t="s">
+        <v>14</v>
+      </c>
+      <c r="G335">
+        <v>8</v>
+      </c>
+      <c r="H335">
+        <v>27</v>
+      </c>
+      <c r="I335">
+        <v>2</v>
+      </c>
+      <c r="J335" t="s">
+        <v>15</v>
+      </c>
+      <c r="K335" t="s">
+        <v>15</v>
+      </c>
+      <c r="L335" t="s">
+        <v>15</v>
+      </c>
+      <c r="M335">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <v>2026</v>
+      </c>
+      <c r="B336">
+        <v>5</v>
+      </c>
+      <c r="C336" t="s">
+        <v>61</v>
+      </c>
+      <c r="D336">
+        <v>427</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+      <c r="F336" t="s">
+        <v>14</v>
+      </c>
+      <c r="G336">
+        <v>8</v>
+      </c>
+      <c r="H336">
+        <v>29</v>
+      </c>
+      <c r="I336">
+        <v>8</v>
+      </c>
+      <c r="J336" t="s">
+        <v>15</v>
+      </c>
+      <c r="K336" t="s">
+        <v>15</v>
+      </c>
+      <c r="L336" t="s">
+        <v>15</v>
+      </c>
+      <c r="M336">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <v>2026</v>
+      </c>
+      <c r="B337">
+        <v>5</v>
+      </c>
+      <c r="C337" t="s">
+        <v>61</v>
+      </c>
+      <c r="D337">
+        <v>427</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+      <c r="F337" t="s">
+        <v>14</v>
+      </c>
+      <c r="G337">
+        <v>8</v>
+      </c>
+      <c r="H337">
+        <v>32</v>
+      </c>
+      <c r="I337">
+        <v>5</v>
+      </c>
+      <c r="J337" t="s">
+        <v>15</v>
+      </c>
+      <c r="K337" t="s">
+        <v>15</v>
+      </c>
+      <c r="L337" t="s">
+        <v>15</v>
+      </c>
+      <c r="M337">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <v>2026</v>
+      </c>
+      <c r="B338">
+        <v>5</v>
+      </c>
+      <c r="C338" t="s">
+        <v>61</v>
+      </c>
+      <c r="D338">
+        <v>427</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+      <c r="F338" t="s">
+        <v>14</v>
+      </c>
+      <c r="G338">
+        <v>8</v>
+      </c>
+      <c r="H338">
+        <v>24</v>
+      </c>
+      <c r="I338">
+        <v>1</v>
+      </c>
+      <c r="J338" t="s">
+        <v>15</v>
+      </c>
+      <c r="K338" t="s">
+        <v>15</v>
+      </c>
+      <c r="L338" t="s">
+        <v>15</v>
+      </c>
+      <c r="M338">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <v>2026</v>
+      </c>
+      <c r="B339">
+        <v>5</v>
+      </c>
+      <c r="C339" t="s">
+        <v>61</v>
+      </c>
+      <c r="D339">
+        <v>427</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+      <c r="F339" t="s">
+        <v>14</v>
+      </c>
+      <c r="G339">
+        <v>8</v>
+      </c>
+      <c r="H339">
+        <v>31</v>
+      </c>
+      <c r="I339">
+        <v>5</v>
+      </c>
+      <c r="J339" t="s">
+        <v>15</v>
+      </c>
+      <c r="K339" t="s">
+        <v>15</v>
+      </c>
+      <c r="L339" t="s">
+        <v>15</v>
+      </c>
+      <c r="M339">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>2026</v>
+      </c>
+      <c r="B340">
+        <v>5</v>
+      </c>
+      <c r="C340" t="s">
+        <v>61</v>
+      </c>
+      <c r="D340">
+        <v>427</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+      <c r="F340" t="s">
+        <v>14</v>
+      </c>
+      <c r="G340">
+        <v>8</v>
+      </c>
+      <c r="H340">
+        <v>23</v>
+      </c>
+      <c r="I340">
+        <v>2</v>
+      </c>
+      <c r="J340" t="s">
+        <v>15</v>
+      </c>
+      <c r="K340" t="s">
+        <v>15</v>
+      </c>
+      <c r="L340" t="s">
+        <v>15</v>
+      </c>
+      <c r="M340">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>2026</v>
+      </c>
+      <c r="B341">
+        <v>5</v>
+      </c>
+      <c r="C341" t="s">
+        <v>61</v>
+      </c>
+      <c r="D341">
+        <v>427</v>
+      </c>
+      <c r="E341">
+        <v>1</v>
+      </c>
+      <c r="F341" t="s">
+        <v>14</v>
+      </c>
+      <c r="G341">
+        <v>8</v>
+      </c>
+      <c r="H341">
+        <v>30</v>
+      </c>
+      <c r="I341">
+        <v>2</v>
+      </c>
+      <c r="J341" t="s">
+        <v>15</v>
+      </c>
+      <c r="K341" t="s">
+        <v>15</v>
+      </c>
+      <c r="L341" t="s">
+        <v>15</v>
+      </c>
+      <c r="M341">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <v>2026</v>
+      </c>
+      <c r="B342">
+        <v>5</v>
+      </c>
+      <c r="C342" t="s">
+        <v>61</v>
+      </c>
+      <c r="D342">
+        <v>427</v>
+      </c>
+      <c r="E342">
+        <v>1</v>
+      </c>
+      <c r="F342" t="s">
+        <v>14</v>
+      </c>
+      <c r="G342">
+        <v>0</v>
+      </c>
+      <c r="H342">
+        <v>42</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342" t="s">
+        <v>15</v>
+      </c>
+      <c r="K342" t="s">
+        <v>15</v>
+      </c>
+      <c r="L342" t="s">
+        <v>15</v>
+      </c>
+      <c r="M342">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <v>2026</v>
+      </c>
+      <c r="B343">
+        <v>5</v>
+      </c>
+      <c r="C343" t="s">
+        <v>61</v>
+      </c>
+      <c r="D343">
+        <v>427</v>
+      </c>
+      <c r="E343">
+        <v>1</v>
+      </c>
+      <c r="F343" t="s">
+        <v>14</v>
+      </c>
+      <c r="G343">
+        <v>8</v>
+      </c>
+      <c r="H343">
+        <v>38</v>
+      </c>
+      <c r="I343">
+        <v>1</v>
+      </c>
+      <c r="J343" t="s">
+        <v>15</v>
+      </c>
+      <c r="K343" t="s">
+        <v>15</v>
+      </c>
+      <c r="L343" t="s">
+        <v>15</v>
+      </c>
+      <c r="M343">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <v>2026</v>
+      </c>
+      <c r="B344">
+        <v>5</v>
+      </c>
+      <c r="C344" t="s">
+        <v>61</v>
+      </c>
+      <c r="D344">
+        <v>427</v>
+      </c>
+      <c r="E344">
+        <v>1</v>
+      </c>
+      <c r="F344" t="s">
+        <v>14</v>
+      </c>
+      <c r="G344">
+        <v>8</v>
+      </c>
+      <c r="H344">
+        <v>28</v>
+      </c>
+      <c r="I344">
+        <v>5</v>
+      </c>
+      <c r="J344" t="s">
+        <v>15</v>
+      </c>
+      <c r="K344" t="s">
+        <v>15</v>
+      </c>
+      <c r="L344" t="s">
+        <v>15</v>
+      </c>
+      <c r="M344">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <v>2026</v>
+      </c>
+      <c r="B345">
+        <v>5</v>
+      </c>
+      <c r="C345" t="s">
+        <v>61</v>
+      </c>
+      <c r="D345">
+        <v>427</v>
+      </c>
+      <c r="E345">
+        <v>1</v>
+      </c>
+      <c r="F345" t="s">
+        <v>14</v>
+      </c>
+      <c r="G345">
+        <v>8</v>
+      </c>
+      <c r="H345">
+        <v>25</v>
+      </c>
+      <c r="I345">
+        <v>1</v>
+      </c>
+      <c r="J345" t="s">
+        <v>15</v>
+      </c>
+      <c r="K345" t="s">
+        <v>15</v>
+      </c>
+      <c r="L345" t="s">
+        <v>15</v>
+      </c>
+      <c r="M345">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>2026</v>
+      </c>
+      <c r="B346">
+        <v>5</v>
+      </c>
+      <c r="C346" t="s">
+        <v>61</v>
+      </c>
+      <c r="D346">
+        <v>427</v>
+      </c>
+      <c r="E346">
+        <v>1</v>
+      </c>
+      <c r="F346" t="s">
+        <v>14</v>
+      </c>
+      <c r="G346">
+        <v>8</v>
+      </c>
+      <c r="H346">
+        <v>26</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346" t="s">
+        <v>15</v>
+      </c>
+      <c r="K346" t="s">
+        <v>15</v>
+      </c>
+      <c r="L346" t="s">
+        <v>15</v>
+      </c>
+      <c r="M346">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>2026</v>
+      </c>
+      <c r="B347">
+        <v>5</v>
+      </c>
+      <c r="C347" t="s">
+        <v>61</v>
+      </c>
+      <c r="D347">
+        <v>427</v>
+      </c>
+      <c r="E347">
+        <v>1</v>
+      </c>
+      <c r="F347" t="s">
+        <v>14</v>
+      </c>
+      <c r="G347">
+        <v>8</v>
+      </c>
+      <c r="H347">
+        <v>37</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347" t="s">
+        <v>15</v>
+      </c>
+      <c r="K347" t="s">
+        <v>15</v>
+      </c>
+      <c r="L347" t="s">
+        <v>15</v>
+      </c>
+      <c r="M347">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>2026</v>
+      </c>
+      <c r="B348">
+        <v>5</v>
+      </c>
+      <c r="C348" t="s">
+        <v>61</v>
+      </c>
+      <c r="D348">
+        <v>427</v>
+      </c>
+      <c r="E348">
+        <v>1</v>
+      </c>
+      <c r="F348" t="s">
+        <v>14</v>
+      </c>
+      <c r="G348">
+        <v>8</v>
+      </c>
+      <c r="H348">
+        <v>35</v>
+      </c>
+      <c r="I348">
+        <v>1</v>
+      </c>
+      <c r="J348" t="s">
+        <v>15</v>
+      </c>
+      <c r="K348" t="s">
+        <v>15</v>
+      </c>
+      <c r="L348" t="s">
+        <v>15</v>
+      </c>
+      <c r="M348">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <v>2026</v>
+      </c>
+      <c r="B349">
+        <v>5</v>
+      </c>
+      <c r="C349" t="s">
+        <v>61</v>
+      </c>
+      <c r="D349">
+        <v>427</v>
+      </c>
+      <c r="E349">
+        <v>1</v>
+      </c>
+      <c r="F349" t="s">
+        <v>14</v>
+      </c>
+      <c r="G349">
+        <v>8</v>
+      </c>
+      <c r="H349">
+        <v>36</v>
+      </c>
+      <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="J349" t="s">
+        <v>15</v>
+      </c>
+      <c r="K349" t="s">
+        <v>15</v>
+      </c>
+      <c r="L349" t="s">
+        <v>15</v>
+      </c>
+      <c r="M349">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <v>2026</v>
+      </c>
+      <c r="B350">
+        <v>5</v>
+      </c>
+      <c r="C350" t="s">
+        <v>61</v>
+      </c>
+      <c r="D350">
+        <v>427</v>
+      </c>
+      <c r="E350">
+        <v>1</v>
+      </c>
+      <c r="F350" t="s">
+        <v>14</v>
+      </c>
+      <c r="H350" t="s">
+        <v>15</v>
+      </c>
+      <c r="I350" t="s">
+        <v>15</v>
+      </c>
+      <c r="J350">
+        <v>45</v>
+      </c>
+      <c r="K350" t="s">
+        <v>15</v>
+      </c>
+      <c r="L350" t="s">
+        <v>15</v>
+      </c>
+      <c r="M350">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <v>2026</v>
+      </c>
+      <c r="B351">
+        <v>5</v>
+      </c>
+      <c r="C351" t="s">
+        <v>61</v>
+      </c>
+      <c r="D351">
+        <v>427</v>
+      </c>
+      <c r="E351">
+        <v>1</v>
+      </c>
+      <c r="F351" t="s">
+        <v>14</v>
+      </c>
+      <c r="G351">
+        <v>0</v>
+      </c>
+      <c r="H351">
+        <v>96</v>
+      </c>
+      <c r="I351">
+        <v>1</v>
+      </c>
+      <c r="J351" t="s">
+        <v>15</v>
+      </c>
+      <c r="K351" t="s">
+        <v>15</v>
+      </c>
+      <c r="L351" t="s">
+        <v>15</v>
+      </c>
+      <c r="M351">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <v>2026</v>
+      </c>
+      <c r="B352">
+        <v>5</v>
+      </c>
+      <c r="C352" t="s">
+        <v>61</v>
+      </c>
+      <c r="D352">
+        <v>427</v>
+      </c>
+      <c r="E352">
+        <v>1</v>
+      </c>
+      <c r="F352" t="s">
+        <v>14</v>
+      </c>
+      <c r="G352">
+        <v>0</v>
+      </c>
+      <c r="H352">
+        <v>84</v>
+      </c>
+      <c r="I352">
+        <v>1</v>
+      </c>
+      <c r="J352" t="s">
+        <v>15</v>
+      </c>
+      <c r="K352" t="s">
+        <v>15</v>
+      </c>
+      <c r="L352" t="s">
+        <v>15</v>
+      </c>
+      <c r="M352">
+        <v>5649.95</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>2026</v>
+      </c>
+      <c r="B353">
+        <v>5</v>
+      </c>
+      <c r="C353" t="s">
+        <v>61</v>
+      </c>
+      <c r="D353">
+        <v>428</v>
+      </c>
+      <c r="E353">
+        <v>1</v>
+      </c>
+      <c r="F353" t="s">
+        <v>14</v>
+      </c>
+      <c r="G353">
+        <v>8</v>
+      </c>
+      <c r="H353">
+        <v>26</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353" t="s">
+        <v>15</v>
+      </c>
+      <c r="K353" t="s">
+        <v>15</v>
+      </c>
+      <c r="L353" t="s">
+        <v>15</v>
+      </c>
+      <c r="M353">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>2026</v>
+      </c>
+      <c r="B354">
+        <v>5</v>
+      </c>
+      <c r="C354" t="s">
+        <v>61</v>
+      </c>
+      <c r="D354">
+        <v>428</v>
+      </c>
+      <c r="E354">
+        <v>1</v>
+      </c>
+      <c r="F354" t="s">
+        <v>14</v>
+      </c>
+      <c r="G354">
+        <v>8</v>
+      </c>
+      <c r="H354">
+        <v>29</v>
+      </c>
+      <c r="I354">
+        <v>8</v>
+      </c>
+      <c r="J354" t="s">
+        <v>15</v>
+      </c>
+      <c r="K354" t="s">
+        <v>15</v>
+      </c>
+      <c r="L354" t="s">
+        <v>15</v>
+      </c>
+      <c r="M354">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>2026</v>
+      </c>
+      <c r="B355">
+        <v>5</v>
+      </c>
+      <c r="C355" t="s">
+        <v>61</v>
+      </c>
+      <c r="D355">
+        <v>428</v>
+      </c>
+      <c r="E355">
+        <v>1</v>
+      </c>
+      <c r="F355" t="s">
+        <v>14</v>
+      </c>
+      <c r="G355">
+        <v>8</v>
+      </c>
+      <c r="H355">
+        <v>30</v>
+      </c>
+      <c r="I355">
+        <v>8</v>
+      </c>
+      <c r="J355" t="s">
+        <v>15</v>
+      </c>
+      <c r="K355" t="s">
+        <v>15</v>
+      </c>
+      <c r="L355" t="s">
+        <v>15</v>
+      </c>
+      <c r="M355">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>2026</v>
+      </c>
+      <c r="B356">
+        <v>5</v>
+      </c>
+      <c r="C356" t="s">
+        <v>61</v>
+      </c>
+      <c r="D356">
+        <v>428</v>
+      </c>
+      <c r="E356">
+        <v>1</v>
+      </c>
+      <c r="F356" t="s">
+        <v>14</v>
+      </c>
+      <c r="G356">
+        <v>8</v>
+      </c>
+      <c r="H356">
+        <v>33</v>
+      </c>
+      <c r="I356">
+        <v>6</v>
+      </c>
+      <c r="J356" t="s">
+        <v>15</v>
+      </c>
+      <c r="K356" t="s">
+        <v>15</v>
+      </c>
+      <c r="L356" t="s">
+        <v>15</v>
+      </c>
+      <c r="M356">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>2026</v>
+      </c>
+      <c r="B357">
+        <v>5</v>
+      </c>
+      <c r="C357" t="s">
+        <v>61</v>
+      </c>
+      <c r="D357">
+        <v>428</v>
+      </c>
+      <c r="E357">
+        <v>1</v>
+      </c>
+      <c r="F357" t="s">
+        <v>14</v>
+      </c>
+      <c r="G357">
+        <v>8</v>
+      </c>
+      <c r="H357">
+        <v>38</v>
+      </c>
+      <c r="I357">
+        <v>1</v>
+      </c>
+      <c r="J357" t="s">
+        <v>15</v>
+      </c>
+      <c r="K357" t="s">
+        <v>15</v>
+      </c>
+      <c r="L357" t="s">
+        <v>15</v>
+      </c>
+      <c r="M357">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>2026</v>
+      </c>
+      <c r="B358">
+        <v>5</v>
+      </c>
+      <c r="C358" t="s">
+        <v>61</v>
+      </c>
+      <c r="D358">
+        <v>428</v>
+      </c>
+      <c r="E358">
+        <v>1</v>
+      </c>
+      <c r="F358" t="s">
+        <v>14</v>
+      </c>
+      <c r="G358">
+        <v>8</v>
+      </c>
+      <c r="H358">
+        <v>31</v>
+      </c>
+      <c r="I358">
+        <v>7</v>
+      </c>
+      <c r="J358" t="s">
+        <v>15</v>
+      </c>
+      <c r="K358" t="s">
+        <v>15</v>
+      </c>
+      <c r="L358" t="s">
+        <v>15</v>
+      </c>
+      <c r="M358">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>2026</v>
+      </c>
+      <c r="B359">
+        <v>5</v>
+      </c>
+      <c r="C359" t="s">
+        <v>61</v>
+      </c>
+      <c r="D359">
+        <v>428</v>
+      </c>
+      <c r="E359">
+        <v>1</v>
+      </c>
+      <c r="F359" t="s">
+        <v>14</v>
+      </c>
+      <c r="G359">
+        <v>8</v>
+      </c>
+      <c r="H359">
+        <v>28</v>
+      </c>
+      <c r="I359">
+        <v>6</v>
+      </c>
+      <c r="J359" t="s">
+        <v>15</v>
+      </c>
+      <c r="K359" t="s">
+        <v>15</v>
+      </c>
+      <c r="L359" t="s">
+        <v>15</v>
+      </c>
+      <c r="M359">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>2026</v>
+      </c>
+      <c r="B360">
+        <v>5</v>
+      </c>
+      <c r="C360" t="s">
+        <v>61</v>
+      </c>
+      <c r="D360">
+        <v>428</v>
+      </c>
+      <c r="E360">
+        <v>1</v>
+      </c>
+      <c r="F360" t="s">
+        <v>14</v>
+      </c>
+      <c r="G360">
+        <v>8</v>
+      </c>
+      <c r="H360">
+        <v>39</v>
+      </c>
+      <c r="I360">
+        <v>1</v>
+      </c>
+      <c r="J360" t="s">
+        <v>15</v>
+      </c>
+      <c r="K360" t="s">
+        <v>15</v>
+      </c>
+      <c r="L360" t="s">
+        <v>15</v>
+      </c>
+      <c r="M360">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>2026</v>
+      </c>
+      <c r="B361">
+        <v>5</v>
+      </c>
+      <c r="C361" t="s">
+        <v>61</v>
+      </c>
+      <c r="D361">
+        <v>428</v>
+      </c>
+      <c r="E361">
+        <v>1</v>
+      </c>
+      <c r="F361" t="s">
+        <v>14</v>
+      </c>
+      <c r="G361">
+        <v>8</v>
+      </c>
+      <c r="H361">
+        <v>32</v>
+      </c>
+      <c r="I361">
+        <v>3</v>
+      </c>
+      <c r="J361" t="s">
+        <v>15</v>
+      </c>
+      <c r="K361" t="s">
+        <v>15</v>
+      </c>
+      <c r="L361" t="s">
+        <v>15</v>
+      </c>
+      <c r="M361">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>2026</v>
+      </c>
+      <c r="B362">
+        <v>5</v>
+      </c>
+      <c r="C362" t="s">
+        <v>61</v>
+      </c>
+      <c r="D362">
+        <v>428</v>
+      </c>
+      <c r="E362">
+        <v>1</v>
+      </c>
+      <c r="F362" t="s">
+        <v>14</v>
+      </c>
+      <c r="G362">
+        <v>8</v>
+      </c>
+      <c r="H362">
+        <v>23</v>
+      </c>
+      <c r="I362">
+        <v>1</v>
+      </c>
+      <c r="J362" t="s">
+        <v>15</v>
+      </c>
+      <c r="K362" t="s">
+        <v>15</v>
+      </c>
+      <c r="L362" t="s">
+        <v>15</v>
+      </c>
+      <c r="M362">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>2026</v>
+      </c>
+      <c r="B363">
+        <v>5</v>
+      </c>
+      <c r="C363" t="s">
+        <v>61</v>
+      </c>
+      <c r="D363">
+        <v>428</v>
+      </c>
+      <c r="E363">
+        <v>1</v>
+      </c>
+      <c r="F363" t="s">
+        <v>14</v>
+      </c>
+      <c r="G363">
+        <v>8</v>
+      </c>
+      <c r="H363">
+        <v>34</v>
+      </c>
+      <c r="I363">
+        <v>3</v>
+      </c>
+      <c r="J363" t="s">
+        <v>15</v>
+      </c>
+      <c r="K363" t="s">
+        <v>15</v>
+      </c>
+      <c r="L363" t="s">
+        <v>15</v>
+      </c>
+      <c r="M363">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>2026</v>
+      </c>
+      <c r="B364">
+        <v>5</v>
+      </c>
+      <c r="C364" t="s">
+        <v>61</v>
+      </c>
+      <c r="D364">
+        <v>428</v>
+      </c>
+      <c r="E364">
+        <v>1</v>
+      </c>
+      <c r="F364" t="s">
+        <v>14</v>
+      </c>
+      <c r="G364">
+        <v>8</v>
+      </c>
+      <c r="H364">
+        <v>35</v>
+      </c>
+      <c r="I364">
+        <v>1</v>
+      </c>
+      <c r="J364" t="s">
+        <v>15</v>
+      </c>
+      <c r="K364" t="s">
+        <v>15</v>
+      </c>
+      <c r="L364" t="s">
+        <v>15</v>
+      </c>
+      <c r="M364">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>2026</v>
+      </c>
+      <c r="B365">
+        <v>5</v>
+      </c>
+      <c r="C365" t="s">
+        <v>61</v>
+      </c>
+      <c r="D365">
+        <v>428</v>
+      </c>
+      <c r="E365">
+        <v>1</v>
+      </c>
+      <c r="F365" t="s">
+        <v>14</v>
+      </c>
+      <c r="G365">
+        <v>8</v>
+      </c>
+      <c r="H365">
+        <v>27</v>
+      </c>
+      <c r="I365">
+        <v>1</v>
+      </c>
+      <c r="J365" t="s">
+        <v>15</v>
+      </c>
+      <c r="K365" t="s">
+        <v>15</v>
+      </c>
+      <c r="L365" t="s">
+        <v>15</v>
+      </c>
+      <c r="M365">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>2026</v>
+      </c>
+      <c r="B366">
+        <v>5</v>
+      </c>
+      <c r="C366" t="s">
+        <v>61</v>
+      </c>
+      <c r="D366">
+        <v>428</v>
+      </c>
+      <c r="E366">
+        <v>1</v>
+      </c>
+      <c r="F366" t="s">
+        <v>14</v>
+      </c>
+      <c r="G366">
+        <v>8</v>
+      </c>
+      <c r="H366">
+        <v>25</v>
+      </c>
+      <c r="I366">
+        <v>2</v>
+      </c>
+      <c r="J366" t="s">
+        <v>15</v>
+      </c>
+      <c r="K366" t="s">
+        <v>15</v>
+      </c>
+      <c r="L366" t="s">
+        <v>15</v>
+      </c>
+      <c r="M366">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>2026</v>
+      </c>
+      <c r="B367">
+        <v>5</v>
+      </c>
+      <c r="C367" t="s">
+        <v>61</v>
+      </c>
+      <c r="D367">
+        <v>428</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+      <c r="F367" t="s">
+        <v>14</v>
+      </c>
+      <c r="G367">
+        <v>8</v>
+      </c>
+      <c r="H367">
+        <v>24</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367" t="s">
+        <v>15</v>
+      </c>
+      <c r="K367" t="s">
+        <v>15</v>
+      </c>
+      <c r="L367" t="s">
+        <v>15</v>
+      </c>
+      <c r="M367">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <v>2026</v>
+      </c>
+      <c r="B368">
+        <v>5</v>
+      </c>
+      <c r="C368" t="s">
+        <v>61</v>
+      </c>
+      <c r="D368">
+        <v>428</v>
+      </c>
+      <c r="E368">
+        <v>1</v>
+      </c>
+      <c r="F368" t="s">
+        <v>14</v>
+      </c>
+      <c r="H368" t="s">
+        <v>15</v>
+      </c>
+      <c r="I368" t="s">
+        <v>15</v>
+      </c>
+      <c r="J368">
+        <v>6</v>
+      </c>
+      <c r="K368" t="s">
+        <v>15</v>
+      </c>
+      <c r="L368" t="s">
+        <v>15</v>
+      </c>
+      <c r="M368">
+        <v>6769.7624999999998</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <v>2026</v>
+      </c>
+      <c r="B369">
+        <v>5</v>
+      </c>
+      <c r="C369" t="s">
+        <v>61</v>
+      </c>
+      <c r="D369">
+        <v>429</v>
+      </c>
+      <c r="E369">
+        <v>2</v>
+      </c>
+      <c r="F369" t="s">
+        <v>14</v>
+      </c>
+      <c r="G369">
+        <v>8</v>
+      </c>
+      <c r="H369">
+        <v>28</v>
+      </c>
+      <c r="I369">
+        <v>1</v>
+      </c>
+      <c r="J369" t="s">
+        <v>15</v>
+      </c>
+      <c r="K369" t="s">
+        <v>15</v>
+      </c>
+      <c r="L369" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M369" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <v>2026</v>
+      </c>
+      <c r="B370">
+        <v>5</v>
+      </c>
+      <c r="C370" t="s">
+        <v>61</v>
+      </c>
+      <c r="D370">
+        <v>429</v>
+      </c>
+      <c r="E370">
+        <v>2</v>
+      </c>
+      <c r="F370" t="s">
+        <v>14</v>
+      </c>
+      <c r="G370">
+        <v>8</v>
+      </c>
+      <c r="H370">
+        <v>27</v>
+      </c>
+      <c r="I370">
+        <v>1</v>
+      </c>
+      <c r="J370" t="s">
+        <v>15</v>
+      </c>
+      <c r="K370" t="s">
+        <v>15</v>
+      </c>
+      <c r="L370" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M370" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <v>2026</v>
+      </c>
+      <c r="B371">
+        <v>5</v>
+      </c>
+      <c r="C371" t="s">
+        <v>61</v>
+      </c>
+      <c r="D371">
+        <v>429</v>
+      </c>
+      <c r="E371">
+        <v>2</v>
+      </c>
+      <c r="F371" t="s">
+        <v>14</v>
+      </c>
+      <c r="G371">
+        <v>8</v>
+      </c>
+      <c r="H371">
+        <v>31</v>
+      </c>
+      <c r="I371">
+        <v>1</v>
+      </c>
+      <c r="J371" t="s">
+        <v>15</v>
+      </c>
+      <c r="K371" t="s">
+        <v>15</v>
+      </c>
+      <c r="L371" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M371" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <v>2026</v>
+      </c>
+      <c r="B372">
+        <v>5</v>
+      </c>
+      <c r="C372" t="s">
+        <v>61</v>
+      </c>
+      <c r="D372">
+        <v>429</v>
+      </c>
+      <c r="E372">
+        <v>2</v>
+      </c>
+      <c r="F372" t="s">
+        <v>14</v>
+      </c>
+      <c r="G372">
+        <v>8</v>
+      </c>
+      <c r="H372">
+        <v>24</v>
+      </c>
+      <c r="I372">
+        <v>1</v>
+      </c>
+      <c r="J372" t="s">
+        <v>15</v>
+      </c>
+      <c r="K372" t="s">
+        <v>15</v>
+      </c>
+      <c r="L372" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M372" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <v>2026</v>
+      </c>
+      <c r="B373">
+        <v>5</v>
+      </c>
+      <c r="C373" t="s">
+        <v>61</v>
+      </c>
+      <c r="D373">
+        <v>429</v>
+      </c>
+      <c r="E373">
+        <v>2</v>
+      </c>
+      <c r="F373" t="s">
+        <v>14</v>
+      </c>
+      <c r="G373">
+        <v>8</v>
+      </c>
+      <c r="H373">
+        <v>23</v>
+      </c>
+      <c r="I373">
+        <v>1</v>
+      </c>
+      <c r="J373" t="s">
+        <v>15</v>
+      </c>
+      <c r="K373" t="s">
+        <v>15</v>
+      </c>
+      <c r="L373" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M373" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <v>2026</v>
+      </c>
+      <c r="B374">
+        <v>5</v>
+      </c>
+      <c r="C374" t="s">
+        <v>61</v>
+      </c>
+      <c r="D374">
+        <v>429</v>
+      </c>
+      <c r="E374">
+        <v>2</v>
+      </c>
+      <c r="F374" t="s">
+        <v>14</v>
+      </c>
+      <c r="G374">
+        <v>8</v>
+      </c>
+      <c r="H374">
+        <v>29</v>
+      </c>
+      <c r="I374">
+        <v>1</v>
+      </c>
+      <c r="J374" t="s">
+        <v>15</v>
+      </c>
+      <c r="K374" t="s">
+        <v>15</v>
+      </c>
+      <c r="L374" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M374" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <v>2026</v>
+      </c>
+      <c r="B375">
+        <v>5</v>
+      </c>
+      <c r="C375" t="s">
+        <v>61</v>
+      </c>
+      <c r="D375">
+        <v>429</v>
+      </c>
+      <c r="E375">
+        <v>2</v>
+      </c>
+      <c r="F375" t="s">
+        <v>14</v>
+      </c>
+      <c r="H375" t="s">
+        <v>15</v>
+      </c>
+      <c r="I375" t="s">
+        <v>15</v>
+      </c>
+      <c r="J375">
+        <v>2</v>
+      </c>
+      <c r="K375" t="s">
+        <v>62</v>
+      </c>
+      <c r="L375" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M375" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <v>2026</v>
+      </c>
+      <c r="B376">
+        <v>5</v>
+      </c>
+      <c r="C376" t="s">
+        <v>61</v>
+      </c>
+      <c r="D376">
+        <v>429</v>
+      </c>
+      <c r="E376">
+        <v>1</v>
+      </c>
+      <c r="F376" t="s">
+        <v>14</v>
+      </c>
+      <c r="G376">
+        <v>8</v>
+      </c>
+      <c r="H376">
+        <v>35</v>
+      </c>
+      <c r="I376">
+        <v>3</v>
+      </c>
+      <c r="J376" t="s">
+        <v>15</v>
+      </c>
+      <c r="K376" t="s">
+        <v>15</v>
+      </c>
+      <c r="L376" t="s">
+        <v>15</v>
+      </c>
+      <c r="M376">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <v>2026</v>
+      </c>
+      <c r="B377">
+        <v>5</v>
+      </c>
+      <c r="C377" t="s">
+        <v>61</v>
+      </c>
+      <c r="D377">
+        <v>429</v>
+      </c>
+      <c r="E377">
+        <v>1</v>
+      </c>
+      <c r="F377" t="s">
+        <v>14</v>
+      </c>
+      <c r="G377">
+        <v>8</v>
+      </c>
+      <c r="H377">
+        <v>30</v>
+      </c>
+      <c r="I377">
+        <v>7</v>
+      </c>
+      <c r="J377" t="s">
+        <v>15</v>
+      </c>
+      <c r="K377" t="s">
+        <v>15</v>
+      </c>
+      <c r="L377" t="s">
+        <v>15</v>
+      </c>
+      <c r="M377">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <v>2026</v>
+      </c>
+      <c r="B378">
+        <v>5</v>
+      </c>
+      <c r="C378" t="s">
+        <v>61</v>
+      </c>
+      <c r="D378">
+        <v>429</v>
+      </c>
+      <c r="E378">
+        <v>1</v>
+      </c>
+      <c r="F378" t="s">
+        <v>14</v>
+      </c>
+      <c r="G378">
+        <v>8</v>
+      </c>
+      <c r="H378">
+        <v>31</v>
+      </c>
+      <c r="I378">
+        <v>3</v>
+      </c>
+      <c r="J378" t="s">
+        <v>15</v>
+      </c>
+      <c r="K378" t="s">
+        <v>15</v>
+      </c>
+      <c r="L378" t="s">
+        <v>15</v>
+      </c>
+      <c r="M378">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <v>2026</v>
+      </c>
+      <c r="B379">
+        <v>5</v>
+      </c>
+      <c r="C379" t="s">
+        <v>61</v>
+      </c>
+      <c r="D379">
+        <v>429</v>
+      </c>
+      <c r="E379">
+        <v>1</v>
+      </c>
+      <c r="F379" t="s">
+        <v>14</v>
+      </c>
+      <c r="G379">
+        <v>8</v>
+      </c>
+      <c r="H379">
+        <v>29</v>
+      </c>
+      <c r="I379">
+        <v>11</v>
+      </c>
+      <c r="J379" t="s">
+        <v>15</v>
+      </c>
+      <c r="K379" t="s">
+        <v>15</v>
+      </c>
+      <c r="L379" t="s">
+        <v>15</v>
+      </c>
+      <c r="M379">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <v>2026</v>
+      </c>
+      <c r="B380">
+        <v>5</v>
+      </c>
+      <c r="C380" t="s">
+        <v>61</v>
+      </c>
+      <c r="D380">
+        <v>429</v>
+      </c>
+      <c r="E380">
+        <v>1</v>
+      </c>
+      <c r="F380" t="s">
+        <v>14</v>
+      </c>
+      <c r="G380">
+        <v>8</v>
+      </c>
+      <c r="H380">
+        <v>34</v>
+      </c>
+      <c r="I380">
+        <v>2</v>
+      </c>
+      <c r="J380" t="s">
+        <v>15</v>
+      </c>
+      <c r="K380" t="s">
+        <v>15</v>
+      </c>
+      <c r="L380" t="s">
+        <v>15</v>
+      </c>
+      <c r="M380">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <v>2026</v>
+      </c>
+      <c r="B381">
+        <v>5</v>
+      </c>
+      <c r="C381" t="s">
+        <v>61</v>
+      </c>
+      <c r="D381">
+        <v>429</v>
+      </c>
+      <c r="E381">
+        <v>1</v>
+      </c>
+      <c r="F381" t="s">
+        <v>14</v>
+      </c>
+      <c r="G381">
+        <v>8</v>
+      </c>
+      <c r="H381">
+        <v>28</v>
+      </c>
+      <c r="I381">
+        <v>5</v>
+      </c>
+      <c r="J381" t="s">
+        <v>15</v>
+      </c>
+      <c r="K381" t="s">
+        <v>15</v>
+      </c>
+      <c r="L381" t="s">
+        <v>15</v>
+      </c>
+      <c r="M381">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <v>2026</v>
+      </c>
+      <c r="B382">
+        <v>5</v>
+      </c>
+      <c r="C382" t="s">
+        <v>61</v>
+      </c>
+      <c r="D382">
+        <v>429</v>
+      </c>
+      <c r="E382">
+        <v>1</v>
+      </c>
+      <c r="F382" t="s">
+        <v>14</v>
+      </c>
+      <c r="G382">
+        <v>8</v>
+      </c>
+      <c r="H382">
+        <v>33</v>
+      </c>
+      <c r="I382">
+        <v>2</v>
+      </c>
+      <c r="J382" t="s">
+        <v>15</v>
+      </c>
+      <c r="K382" t="s">
+        <v>15</v>
+      </c>
+      <c r="L382" t="s">
+        <v>15</v>
+      </c>
+      <c r="M382">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <v>2026</v>
+      </c>
+      <c r="B383">
+        <v>5</v>
+      </c>
+      <c r="C383" t="s">
+        <v>61</v>
+      </c>
+      <c r="D383">
+        <v>429</v>
+      </c>
+      <c r="E383">
+        <v>1</v>
+      </c>
+      <c r="F383" t="s">
+        <v>14</v>
+      </c>
+      <c r="G383">
+        <v>8</v>
+      </c>
+      <c r="H383">
+        <v>32</v>
+      </c>
+      <c r="I383">
+        <v>2</v>
+      </c>
+      <c r="J383" t="s">
+        <v>15</v>
+      </c>
+      <c r="K383" t="s">
+        <v>15</v>
+      </c>
+      <c r="L383" t="s">
+        <v>15</v>
+      </c>
+      <c r="M383">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <v>2026</v>
+      </c>
+      <c r="B384">
+        <v>5</v>
+      </c>
+      <c r="C384" t="s">
+        <v>61</v>
+      </c>
+      <c r="D384">
+        <v>429</v>
+      </c>
+      <c r="E384">
+        <v>1</v>
+      </c>
+      <c r="F384" t="s">
+        <v>14</v>
+      </c>
+      <c r="G384">
+        <v>8</v>
+      </c>
+      <c r="H384">
+        <v>26</v>
+      </c>
+      <c r="I384">
+        <v>4</v>
+      </c>
+      <c r="J384" t="s">
+        <v>15</v>
+      </c>
+      <c r="K384" t="s">
+        <v>15</v>
+      </c>
+      <c r="L384" t="s">
+        <v>15</v>
+      </c>
+      <c r="M384">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <v>2026</v>
+      </c>
+      <c r="B385">
+        <v>5</v>
+      </c>
+      <c r="C385" t="s">
+        <v>61</v>
+      </c>
+      <c r="D385">
+        <v>429</v>
+      </c>
+      <c r="E385">
+        <v>1</v>
+      </c>
+      <c r="F385" t="s">
+        <v>14</v>
+      </c>
+      <c r="G385">
+        <v>8</v>
+      </c>
+      <c r="H385">
+        <v>36</v>
+      </c>
+      <c r="I385">
+        <v>1</v>
+      </c>
+      <c r="J385" t="s">
+        <v>15</v>
+      </c>
+      <c r="K385" t="s">
+        <v>15</v>
+      </c>
+      <c r="L385" t="s">
+        <v>15</v>
+      </c>
+      <c r="M385">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <v>2026</v>
+      </c>
+      <c r="B386">
+        <v>5</v>
+      </c>
+      <c r="C386" t="s">
+        <v>61</v>
+      </c>
+      <c r="D386">
+        <v>429</v>
+      </c>
+      <c r="E386">
+        <v>1</v>
+      </c>
+      <c r="F386" t="s">
+        <v>14</v>
+      </c>
+      <c r="G386">
+        <v>8</v>
+      </c>
+      <c r="H386">
+        <v>37</v>
+      </c>
+      <c r="I386">
+        <v>2</v>
+      </c>
+      <c r="J386" t="s">
+        <v>15</v>
+      </c>
+      <c r="K386" t="s">
+        <v>15</v>
+      </c>
+      <c r="L386" t="s">
+        <v>15</v>
+      </c>
+      <c r="M386">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <v>2026</v>
+      </c>
+      <c r="B387">
+        <v>5</v>
+      </c>
+      <c r="C387" t="s">
+        <v>61</v>
+      </c>
+      <c r="D387">
+        <v>429</v>
+      </c>
+      <c r="E387">
+        <v>1</v>
+      </c>
+      <c r="F387" t="s">
+        <v>14</v>
+      </c>
+      <c r="G387">
+        <v>8</v>
+      </c>
+      <c r="H387">
+        <v>21</v>
+      </c>
+      <c r="I387">
+        <v>1</v>
+      </c>
+      <c r="J387" t="s">
+        <v>15</v>
+      </c>
+      <c r="K387" t="s">
+        <v>15</v>
+      </c>
+      <c r="L387" t="s">
+        <v>15</v>
+      </c>
+      <c r="M387">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <v>2026</v>
+      </c>
+      <c r="B388">
+        <v>5</v>
+      </c>
+      <c r="C388" t="s">
+        <v>61</v>
+      </c>
+      <c r="D388">
+        <v>429</v>
+      </c>
+      <c r="E388">
+        <v>1</v>
+      </c>
+      <c r="F388" t="s">
+        <v>14</v>
+      </c>
+      <c r="G388">
+        <v>8</v>
+      </c>
+      <c r="H388">
+        <v>24</v>
+      </c>
+      <c r="I388">
+        <v>3</v>
+      </c>
+      <c r="J388" t="s">
+        <v>15</v>
+      </c>
+      <c r="K388" t="s">
+        <v>15</v>
+      </c>
+      <c r="L388" t="s">
+        <v>15</v>
+      </c>
+      <c r="M388">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <v>2026</v>
+      </c>
+      <c r="B389">
+        <v>5</v>
+      </c>
+      <c r="C389" t="s">
+        <v>61</v>
+      </c>
+      <c r="D389">
+        <v>429</v>
+      </c>
+      <c r="E389">
+        <v>1</v>
+      </c>
+      <c r="F389" t="s">
+        <v>14</v>
+      </c>
+      <c r="G389">
+        <v>8</v>
+      </c>
+      <c r="H389">
+        <v>25</v>
+      </c>
+      <c r="I389">
+        <v>2</v>
+      </c>
+      <c r="J389" t="s">
+        <v>15</v>
+      </c>
+      <c r="K389" t="s">
+        <v>15</v>
+      </c>
+      <c r="L389" t="s">
+        <v>15</v>
+      </c>
+      <c r="M389">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <v>2026</v>
+      </c>
+      <c r="B390">
+        <v>5</v>
+      </c>
+      <c r="C390" t="s">
+        <v>61</v>
+      </c>
+      <c r="D390">
+        <v>429</v>
+      </c>
+      <c r="E390">
+        <v>1</v>
+      </c>
+      <c r="F390" t="s">
+        <v>14</v>
+      </c>
+      <c r="G390">
+        <v>8</v>
+      </c>
+      <c r="H390">
+        <v>27</v>
+      </c>
+      <c r="I390">
+        <v>1</v>
+      </c>
+      <c r="J390" t="s">
+        <v>15</v>
+      </c>
+      <c r="K390" t="s">
+        <v>15</v>
+      </c>
+      <c r="L390" t="s">
+        <v>15</v>
+      </c>
+      <c r="M390">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <v>2026</v>
+      </c>
+      <c r="B391">
+        <v>5</v>
+      </c>
+      <c r="C391" t="s">
+        <v>61</v>
+      </c>
+      <c r="D391">
+        <v>429</v>
+      </c>
+      <c r="E391">
+        <v>1</v>
+      </c>
+      <c r="F391" t="s">
+        <v>14</v>
+      </c>
+      <c r="G391">
+        <v>8</v>
+      </c>
+      <c r="H391">
+        <v>23</v>
+      </c>
+      <c r="I391">
+        <v>1</v>
+      </c>
+      <c r="J391" t="s">
+        <v>15</v>
+      </c>
+      <c r="K391" t="s">
+        <v>15</v>
+      </c>
+      <c r="L391" t="s">
+        <v>15</v>
+      </c>
+      <c r="M391">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A392">
+        <v>2026</v>
+      </c>
+      <c r="B392">
+        <v>5</v>
+      </c>
+      <c r="C392" t="s">
+        <v>61</v>
+      </c>
+      <c r="D392">
+        <v>429</v>
+      </c>
+      <c r="E392">
+        <v>1</v>
+      </c>
+      <c r="F392" t="s">
+        <v>14</v>
+      </c>
+      <c r="H392" t="s">
+        <v>15</v>
+      </c>
+      <c r="I392" t="s">
+        <v>15</v>
+      </c>
+      <c r="J392">
+        <v>16</v>
+      </c>
+      <c r="K392" t="s">
+        <v>15</v>
+      </c>
+      <c r="L392" t="s">
+        <v>15</v>
+      </c>
+      <c r="M392">
+        <v>6357.7749999999996</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A393">
+        <v>2026</v>
+      </c>
+      <c r="B393">
+        <v>5</v>
+      </c>
+      <c r="C393" t="s">
+        <v>61</v>
+      </c>
+      <c r="D393">
+        <v>431</v>
+      </c>
+      <c r="E393">
+        <v>1</v>
+      </c>
+      <c r="F393" t="s">
+        <v>14</v>
+      </c>
+      <c r="G393">
+        <v>8</v>
+      </c>
+      <c r="H393">
+        <v>31</v>
+      </c>
+      <c r="I393">
+        <v>1</v>
+      </c>
+      <c r="J393" t="s">
+        <v>15</v>
+      </c>
+      <c r="K393" t="s">
+        <v>15</v>
+      </c>
+      <c r="L393" t="s">
+        <v>15</v>
+      </c>
+      <c r="M393">
+        <v>7348.2124999999996</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A394">
+        <v>2026</v>
+      </c>
+      <c r="B394">
+        <v>5</v>
+      </c>
+      <c r="C394" t="s">
+        <v>61</v>
+      </c>
+      <c r="D394">
+        <v>431</v>
+      </c>
+      <c r="E394">
+        <v>1</v>
+      </c>
+      <c r="F394" t="s">
+        <v>14</v>
+      </c>
+      <c r="G394">
+        <v>8</v>
+      </c>
+      <c r="H394">
+        <v>27</v>
+      </c>
+      <c r="I394">
+        <v>2</v>
+      </c>
+      <c r="J394" t="s">
+        <v>15</v>
+      </c>
+      <c r="K394" t="s">
+        <v>15</v>
+      </c>
+      <c r="L394" t="s">
+        <v>15</v>
+      </c>
+      <c r="M394">
+        <v>7348.2124999999996</v>
+      </c>
+    </row>
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A395">
+        <v>2026</v>
+      </c>
+      <c r="B395">
+        <v>5</v>
+      </c>
+      <c r="C395" t="s">
+        <v>61</v>
+      </c>
+      <c r="D395">
+        <v>431</v>
+      </c>
+      <c r="E395">
+        <v>1</v>
+      </c>
+      <c r="F395" t="s">
+        <v>14</v>
+      </c>
+      <c r="G395">
+        <v>8</v>
+      </c>
+      <c r="H395">
+        <v>26</v>
+      </c>
+      <c r="I395">
+        <v>1</v>
+      </c>
+      <c r="J395" t="s">
+        <v>15</v>
+      </c>
+      <c r="K395" t="s">
+        <v>15</v>
+      </c>
+      <c r="L395" t="s">
+        <v>15</v>
+      </c>
+      <c r="M395">
+        <v>7348.2124999999996</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A396">
+        <v>2026</v>
+      </c>
+      <c r="B396">
+        <v>5</v>
+      </c>
+      <c r="C396" t="s">
+        <v>61</v>
+      </c>
+      <c r="D396">
+        <v>431</v>
+      </c>
+      <c r="E396">
+        <v>1</v>
+      </c>
+      <c r="F396" t="s">
+        <v>14</v>
+      </c>
+      <c r="G396">
+        <v>8</v>
+      </c>
+      <c r="H396">
+        <v>28</v>
+      </c>
+      <c r="I396">
+        <v>1</v>
+      </c>
+      <c r="J396" t="s">
+        <v>15</v>
+      </c>
+      <c r="K396" t="s">
+        <v>15</v>
+      </c>
+      <c r="L396" t="s">
+        <v>15</v>
+      </c>
+      <c r="M396">
+        <v>7348.2124999999996</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A397">
+        <v>2026</v>
+      </c>
+      <c r="B397">
+        <v>5</v>
+      </c>
+      <c r="C397" t="s">
+        <v>61</v>
+      </c>
+      <c r="D397">
+        <v>431</v>
+      </c>
+      <c r="E397">
+        <v>2</v>
+      </c>
+      <c r="F397" t="s">
+        <v>14</v>
+      </c>
+      <c r="G397">
+        <v>8</v>
+      </c>
+      <c r="H397">
+        <v>32</v>
+      </c>
+      <c r="I397">
+        <v>1</v>
+      </c>
+      <c r="J397" t="s">
+        <v>15</v>
+      </c>
+      <c r="K397" t="s">
+        <v>15</v>
+      </c>
+      <c r="L397" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M397" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A398">
+        <v>2026</v>
+      </c>
+      <c r="B398">
+        <v>5</v>
+      </c>
+      <c r="C398" t="s">
+        <v>61</v>
+      </c>
+      <c r="D398">
+        <v>432</v>
+      </c>
+      <c r="E398">
+        <v>2</v>
+      </c>
+      <c r="F398" t="s">
+        <v>14</v>
+      </c>
+      <c r="G398">
+        <v>8</v>
+      </c>
+      <c r="H398">
+        <v>22</v>
+      </c>
+      <c r="I398">
+        <v>1</v>
+      </c>
+      <c r="J398" t="s">
+        <v>15</v>
+      </c>
+      <c r="K398" t="s">
+        <v>15</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M398" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A399">
+        <v>2026</v>
+      </c>
+      <c r="B399">
+        <v>5</v>
+      </c>
+      <c r="C399" t="s">
+        <v>61</v>
+      </c>
+      <c r="D399">
+        <v>432</v>
+      </c>
+      <c r="E399">
+        <v>2</v>
+      </c>
+      <c r="F399" t="s">
+        <v>14</v>
+      </c>
+      <c r="G399">
+        <v>8</v>
+      </c>
+      <c r="H399">
+        <v>32</v>
+      </c>
+      <c r="I399">
+        <v>1</v>
+      </c>
+      <c r="J399" t="s">
+        <v>15</v>
+      </c>
+      <c r="K399" t="s">
+        <v>15</v>
+      </c>
+      <c r="L399" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M399" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A400">
+        <v>2026</v>
+      </c>
+      <c r="B400">
+        <v>5</v>
+      </c>
+      <c r="C400" t="s">
+        <v>61</v>
+      </c>
+      <c r="D400">
+        <v>432</v>
+      </c>
+      <c r="E400">
+        <v>2</v>
+      </c>
+      <c r="F400" t="s">
+        <v>14</v>
+      </c>
+      <c r="G400">
+        <v>8</v>
+      </c>
+      <c r="H400">
+        <v>29</v>
+      </c>
+      <c r="I400">
+        <v>1</v>
+      </c>
+      <c r="J400" t="s">
+        <v>15</v>
+      </c>
+      <c r="K400" t="s">
+        <v>15</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M400" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A401">
+        <v>2026</v>
+      </c>
+      <c r="B401">
+        <v>5</v>
+      </c>
+      <c r="C401" t="s">
+        <v>61</v>
+      </c>
+      <c r="D401">
+        <v>432</v>
+      </c>
+      <c r="E401">
+        <v>2</v>
+      </c>
+      <c r="F401" t="s">
+        <v>14</v>
+      </c>
+      <c r="G401">
+        <v>8</v>
+      </c>
+      <c r="H401">
+        <v>27</v>
+      </c>
+      <c r="I401">
+        <v>1</v>
+      </c>
+      <c r="J401" t="s">
+        <v>15</v>
+      </c>
+      <c r="K401" t="s">
+        <v>15</v>
+      </c>
+      <c r="L401" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M401" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>2026</v>
+      </c>
+      <c r="B402">
+        <v>5</v>
+      </c>
+      <c r="C402" t="s">
+        <v>61</v>
+      </c>
+      <c r="D402">
+        <v>432</v>
+      </c>
+      <c r="E402">
+        <v>2</v>
+      </c>
+      <c r="F402" t="s">
+        <v>14</v>
+      </c>
+      <c r="G402">
+        <v>8</v>
+      </c>
+      <c r="H402">
+        <v>25</v>
+      </c>
+      <c r="I402">
+        <v>1</v>
+      </c>
+      <c r="J402" t="s">
+        <v>15</v>
+      </c>
+      <c r="K402" t="s">
+        <v>15</v>
+      </c>
+      <c r="L402" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M402" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>2026</v>
+      </c>
+      <c r="B403">
+        <v>5</v>
+      </c>
+      <c r="C403" t="s">
+        <v>61</v>
+      </c>
+      <c r="D403">
+        <v>432</v>
+      </c>
+      <c r="E403">
+        <v>1</v>
+      </c>
+      <c r="F403" t="s">
+        <v>14</v>
+      </c>
+      <c r="G403">
+        <v>8</v>
+      </c>
+      <c r="H403">
+        <v>27</v>
+      </c>
+      <c r="I403">
+        <v>3</v>
+      </c>
+      <c r="J403" t="s">
+        <v>15</v>
+      </c>
+      <c r="K403" t="s">
+        <v>15</v>
+      </c>
+      <c r="L403" t="s">
+        <v>15</v>
+      </c>
+      <c r="M403">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>2026</v>
+      </c>
+      <c r="B404">
+        <v>5</v>
+      </c>
+      <c r="C404" t="s">
+        <v>61</v>
+      </c>
+      <c r="D404">
+        <v>432</v>
+      </c>
+      <c r="E404">
+        <v>1</v>
+      </c>
+      <c r="F404" t="s">
+        <v>14</v>
+      </c>
+      <c r="G404">
+        <v>8</v>
+      </c>
+      <c r="H404">
+        <v>23</v>
+      </c>
+      <c r="I404">
+        <v>1</v>
+      </c>
+      <c r="J404" t="s">
+        <v>15</v>
+      </c>
+      <c r="K404" t="s">
+        <v>15</v>
+      </c>
+      <c r="L404" t="s">
+        <v>15</v>
+      </c>
+      <c r="M404">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>2026</v>
+      </c>
+      <c r="B405">
+        <v>5</v>
+      </c>
+      <c r="C405" t="s">
+        <v>61</v>
+      </c>
+      <c r="D405">
+        <v>432</v>
+      </c>
+      <c r="E405">
+        <v>1</v>
+      </c>
+      <c r="F405" t="s">
+        <v>14</v>
+      </c>
+      <c r="G405">
+        <v>8</v>
+      </c>
+      <c r="H405">
+        <v>28</v>
+      </c>
+      <c r="I405">
+        <v>5</v>
+      </c>
+      <c r="J405" t="s">
+        <v>15</v>
+      </c>
+      <c r="K405" t="s">
+        <v>15</v>
+      </c>
+      <c r="L405" t="s">
+        <v>15</v>
+      </c>
+      <c r="M405">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>2026</v>
+      </c>
+      <c r="B406">
+        <v>5</v>
+      </c>
+      <c r="C406" t="s">
+        <v>61</v>
+      </c>
+      <c r="D406">
+        <v>432</v>
+      </c>
+      <c r="E406">
+        <v>1</v>
+      </c>
+      <c r="F406" t="s">
+        <v>14</v>
+      </c>
+      <c r="G406">
+        <v>8</v>
+      </c>
+      <c r="H406">
+        <v>33</v>
+      </c>
+      <c r="I406">
+        <v>1</v>
+      </c>
+      <c r="J406" t="s">
+        <v>15</v>
+      </c>
+      <c r="K406" t="s">
+        <v>15</v>
+      </c>
+      <c r="L406" t="s">
+        <v>15</v>
+      </c>
+      <c r="M406">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>2026</v>
+      </c>
+      <c r="B407">
+        <v>5</v>
+      </c>
+      <c r="C407" t="s">
+        <v>61</v>
+      </c>
+      <c r="D407">
+        <v>432</v>
+      </c>
+      <c r="E407">
+        <v>1</v>
+      </c>
+      <c r="F407" t="s">
+        <v>14</v>
+      </c>
+      <c r="G407">
+        <v>8</v>
+      </c>
+      <c r="H407">
+        <v>35</v>
+      </c>
+      <c r="I407">
+        <v>2</v>
+      </c>
+      <c r="J407" t="s">
+        <v>15</v>
+      </c>
+      <c r="K407" t="s">
+        <v>15</v>
+      </c>
+      <c r="L407" t="s">
+        <v>15</v>
+      </c>
+      <c r="M407">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>2026</v>
+      </c>
+      <c r="B408">
+        <v>5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>61</v>
+      </c>
+      <c r="D408">
+        <v>432</v>
+      </c>
+      <c r="E408">
+        <v>1</v>
+      </c>
+      <c r="F408" t="s">
+        <v>14</v>
+      </c>
+      <c r="G408">
+        <v>8</v>
+      </c>
+      <c r="H408">
+        <v>37</v>
+      </c>
+      <c r="I408">
+        <v>1</v>
+      </c>
+      <c r="J408" t="s">
+        <v>15</v>
+      </c>
+      <c r="K408" t="s">
+        <v>15</v>
+      </c>
+      <c r="L408" t="s">
+        <v>15</v>
+      </c>
+      <c r="M408">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>2026</v>
+      </c>
+      <c r="B409">
+        <v>5</v>
+      </c>
+      <c r="C409" t="s">
+        <v>61</v>
+      </c>
+      <c r="D409">
+        <v>432</v>
+      </c>
+      <c r="E409">
+        <v>1</v>
+      </c>
+      <c r="F409" t="s">
+        <v>14</v>
+      </c>
+      <c r="G409">
+        <v>8</v>
+      </c>
+      <c r="H409">
+        <v>32</v>
+      </c>
+      <c r="I409">
+        <v>2</v>
+      </c>
+      <c r="J409" t="s">
+        <v>15</v>
+      </c>
+      <c r="K409" t="s">
+        <v>15</v>
+      </c>
+      <c r="L409" t="s">
+        <v>15</v>
+      </c>
+      <c r="M409">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>2026</v>
+      </c>
+      <c r="B410">
+        <v>5</v>
+      </c>
+      <c r="C410" t="s">
+        <v>61</v>
+      </c>
+      <c r="D410">
+        <v>432</v>
+      </c>
+      <c r="E410">
+        <v>1</v>
+      </c>
+      <c r="F410" t="s">
+        <v>14</v>
+      </c>
+      <c r="G410">
+        <v>8</v>
+      </c>
+      <c r="H410">
+        <v>26</v>
+      </c>
+      <c r="I410">
+        <v>3</v>
+      </c>
+      <c r="J410" t="s">
+        <v>15</v>
+      </c>
+      <c r="K410" t="s">
+        <v>15</v>
+      </c>
+      <c r="L410" t="s">
+        <v>15</v>
+      </c>
+      <c r="M410">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>2026</v>
+      </c>
+      <c r="B411">
+        <v>5</v>
+      </c>
+      <c r="C411" t="s">
+        <v>61</v>
+      </c>
+      <c r="D411">
+        <v>432</v>
+      </c>
+      <c r="E411">
+        <v>1</v>
+      </c>
+      <c r="F411" t="s">
+        <v>14</v>
+      </c>
+      <c r="G411">
+        <v>8</v>
+      </c>
+      <c r="H411">
+        <v>25</v>
+      </c>
+      <c r="I411">
+        <v>2</v>
+      </c>
+      <c r="J411" t="s">
+        <v>15</v>
+      </c>
+      <c r="K411" t="s">
+        <v>15</v>
+      </c>
+      <c r="L411" t="s">
+        <v>15</v>
+      </c>
+      <c r="M411">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A412">
+        <v>2026</v>
+      </c>
+      <c r="B412">
+        <v>5</v>
+      </c>
+      <c r="C412" t="s">
+        <v>61</v>
+      </c>
+      <c r="D412">
+        <v>432</v>
+      </c>
+      <c r="E412">
+        <v>1</v>
+      </c>
+      <c r="F412" t="s">
+        <v>14</v>
+      </c>
+      <c r="G412">
+        <v>8</v>
+      </c>
+      <c r="H412">
+        <v>30</v>
+      </c>
+      <c r="I412">
+        <v>3</v>
+      </c>
+      <c r="J412" t="s">
+        <v>15</v>
+      </c>
+      <c r="K412" t="s">
+        <v>15</v>
+      </c>
+      <c r="L412" t="s">
+        <v>15</v>
+      </c>
+      <c r="M412">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A413">
+        <v>2026</v>
+      </c>
+      <c r="B413">
+        <v>5</v>
+      </c>
+      <c r="C413" t="s">
+        <v>61</v>
+      </c>
+      <c r="D413">
+        <v>432</v>
+      </c>
+      <c r="E413">
+        <v>1</v>
+      </c>
+      <c r="F413" t="s">
+        <v>14</v>
+      </c>
+      <c r="G413">
+        <v>8</v>
+      </c>
+      <c r="H413">
+        <v>29</v>
+      </c>
+      <c r="I413">
+        <v>1</v>
+      </c>
+      <c r="J413" t="s">
+        <v>15</v>
+      </c>
+      <c r="K413" t="s">
+        <v>15</v>
+      </c>
+      <c r="L413" t="s">
+        <v>15</v>
+      </c>
+      <c r="M413">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A414">
+        <v>2026</v>
+      </c>
+      <c r="B414">
+        <v>5</v>
+      </c>
+      <c r="C414" t="s">
+        <v>61</v>
+      </c>
+      <c r="D414">
+        <v>432</v>
+      </c>
+      <c r="E414">
+        <v>1</v>
+      </c>
+      <c r="F414" t="s">
+        <v>14</v>
+      </c>
+      <c r="G414">
+        <v>8</v>
+      </c>
+      <c r="H414">
+        <v>31</v>
+      </c>
+      <c r="I414">
+        <v>1</v>
+      </c>
+      <c r="J414" t="s">
+        <v>15</v>
+      </c>
+      <c r="K414" t="s">
+        <v>15</v>
+      </c>
+      <c r="L414" t="s">
+        <v>15</v>
+      </c>
+      <c r="M414">
+        <v>6814.0375000000004</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A415">
+        <v>2026</v>
+      </c>
+      <c r="B415">
+        <v>5</v>
+      </c>
+      <c r="C415" t="s">
+        <v>61</v>
+      </c>
+      <c r="D415">
+        <v>433</v>
+      </c>
+      <c r="E415">
+        <v>1</v>
+      </c>
+      <c r="F415" t="s">
+        <v>14</v>
+      </c>
+      <c r="G415">
+        <v>8</v>
+      </c>
+      <c r="H415">
+        <v>31</v>
+      </c>
+      <c r="I415">
+        <v>1</v>
+      </c>
+      <c r="J415" t="s">
+        <v>15</v>
+      </c>
+      <c r="K415" t="s">
+        <v>15</v>
+      </c>
+      <c r="L415" t="s">
+        <v>15</v>
+      </c>
+      <c r="M415">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A416">
+        <v>2026</v>
+      </c>
+      <c r="B416">
+        <v>5</v>
+      </c>
+      <c r="C416" t="s">
+        <v>61</v>
+      </c>
+      <c r="D416">
+        <v>433</v>
+      </c>
+      <c r="E416">
+        <v>1</v>
+      </c>
+      <c r="F416" t="s">
+        <v>14</v>
+      </c>
+      <c r="G416">
+        <v>8</v>
+      </c>
+      <c r="H416">
+        <v>34</v>
+      </c>
+      <c r="I416">
+        <v>1</v>
+      </c>
+      <c r="J416" t="s">
+        <v>15</v>
+      </c>
+      <c r="K416" t="s">
+        <v>15</v>
+      </c>
+      <c r="L416" t="s">
+        <v>15</v>
+      </c>
+      <c r="M416">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A417">
+        <v>2026</v>
+      </c>
+      <c r="B417">
+        <v>5</v>
+      </c>
+      <c r="C417" t="s">
+        <v>61</v>
+      </c>
+      <c r="D417">
+        <v>433</v>
+      </c>
+      <c r="E417">
+        <v>1</v>
+      </c>
+      <c r="F417" t="s">
+        <v>14</v>
+      </c>
+      <c r="G417">
+        <v>8</v>
+      </c>
+      <c r="H417">
+        <v>32</v>
+      </c>
+      <c r="I417">
+        <v>6</v>
+      </c>
+      <c r="J417" t="s">
+        <v>15</v>
+      </c>
+      <c r="K417" t="s">
+        <v>15</v>
+      </c>
+      <c r="L417" t="s">
+        <v>15</v>
+      </c>
+      <c r="M417">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A418">
+        <v>2026</v>
+      </c>
+      <c r="B418">
+        <v>5</v>
+      </c>
+      <c r="C418" t="s">
+        <v>61</v>
+      </c>
+      <c r="D418">
+        <v>433</v>
+      </c>
+      <c r="E418">
+        <v>1</v>
+      </c>
+      <c r="F418" t="s">
+        <v>14</v>
+      </c>
+      <c r="G418">
+        <v>8</v>
+      </c>
+      <c r="H418">
+        <v>30</v>
+      </c>
+      <c r="I418">
+        <v>3</v>
+      </c>
+      <c r="J418" t="s">
+        <v>15</v>
+      </c>
+      <c r="K418" t="s">
+        <v>15</v>
+      </c>
+      <c r="L418" t="s">
+        <v>15</v>
+      </c>
+      <c r="M418">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>2026</v>
+      </c>
+      <c r="B419">
+        <v>5</v>
+      </c>
+      <c r="C419" t="s">
+        <v>61</v>
+      </c>
+      <c r="D419">
+        <v>433</v>
+      </c>
+      <c r="E419">
+        <v>1</v>
+      </c>
+      <c r="F419" t="s">
+        <v>14</v>
+      </c>
+      <c r="G419">
+        <v>8</v>
+      </c>
+      <c r="H419">
+        <v>28</v>
+      </c>
+      <c r="I419">
+        <v>2</v>
+      </c>
+      <c r="J419" t="s">
+        <v>15</v>
+      </c>
+      <c r="K419" t="s">
+        <v>15</v>
+      </c>
+      <c r="L419" t="s">
+        <v>15</v>
+      </c>
+      <c r="M419">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>2026</v>
+      </c>
+      <c r="B420">
+        <v>5</v>
+      </c>
+      <c r="C420" t="s">
+        <v>61</v>
+      </c>
+      <c r="D420">
+        <v>433</v>
+      </c>
+      <c r="E420">
+        <v>1</v>
+      </c>
+      <c r="F420" t="s">
+        <v>14</v>
+      </c>
+      <c r="G420">
+        <v>8</v>
+      </c>
+      <c r="H420">
+        <v>29</v>
+      </c>
+      <c r="I420">
+        <v>4</v>
+      </c>
+      <c r="J420" t="s">
+        <v>15</v>
+      </c>
+      <c r="K420" t="s">
+        <v>15</v>
+      </c>
+      <c r="L420" t="s">
+        <v>15</v>
+      </c>
+      <c r="M420">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>2026</v>
+      </c>
+      <c r="B421">
+        <v>5</v>
+      </c>
+      <c r="C421" t="s">
+        <v>61</v>
+      </c>
+      <c r="D421">
+        <v>433</v>
+      </c>
+      <c r="E421">
+        <v>1</v>
+      </c>
+      <c r="F421" t="s">
+        <v>14</v>
+      </c>
+      <c r="G421">
+        <v>8</v>
+      </c>
+      <c r="H421">
+        <v>26</v>
+      </c>
+      <c r="I421">
+        <v>1</v>
+      </c>
+      <c r="J421" t="s">
+        <v>15</v>
+      </c>
+      <c r="K421" t="s">
+        <v>15</v>
+      </c>
+      <c r="L421" t="s">
+        <v>15</v>
+      </c>
+      <c r="M421">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A422">
+        <v>2026</v>
+      </c>
+      <c r="B422">
+        <v>5</v>
+      </c>
+      <c r="C422" t="s">
+        <v>61</v>
+      </c>
+      <c r="D422">
+        <v>433</v>
+      </c>
+      <c r="E422">
+        <v>1</v>
+      </c>
+      <c r="F422" t="s">
+        <v>14</v>
+      </c>
+      <c r="G422">
+        <v>8</v>
+      </c>
+      <c r="H422">
+        <v>33</v>
+      </c>
+      <c r="I422">
+        <v>1</v>
+      </c>
+      <c r="J422" t="s">
+        <v>15</v>
+      </c>
+      <c r="K422" t="s">
+        <v>15</v>
+      </c>
+      <c r="L422" t="s">
+        <v>15</v>
+      </c>
+      <c r="M422">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A423">
+        <v>2026</v>
+      </c>
+      <c r="B423">
+        <v>5</v>
+      </c>
+      <c r="C423" t="s">
+        <v>61</v>
+      </c>
+      <c r="D423">
+        <v>433</v>
+      </c>
+      <c r="E423">
+        <v>1</v>
+      </c>
+      <c r="F423" t="s">
+        <v>14</v>
+      </c>
+      <c r="G423">
+        <v>8</v>
+      </c>
+      <c r="H423">
+        <v>24</v>
+      </c>
+      <c r="I423">
+        <v>2</v>
+      </c>
+      <c r="J423" t="s">
+        <v>15</v>
+      </c>
+      <c r="K423" t="s">
+        <v>15</v>
+      </c>
+      <c r="L423" t="s">
+        <v>15</v>
+      </c>
+      <c r="M423">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A424">
+        <v>2026</v>
+      </c>
+      <c r="B424">
+        <v>5</v>
+      </c>
+      <c r="C424" t="s">
+        <v>61</v>
+      </c>
+      <c r="D424">
+        <v>433</v>
+      </c>
+      <c r="E424">
+        <v>1</v>
+      </c>
+      <c r="F424" t="s">
+        <v>14</v>
+      </c>
+      <c r="G424">
+        <v>8</v>
+      </c>
+      <c r="H424">
+        <v>22</v>
+      </c>
+      <c r="I424">
+        <v>1</v>
+      </c>
+      <c r="J424" t="s">
+        <v>15</v>
+      </c>
+      <c r="K424" t="s">
+        <v>15</v>
+      </c>
+      <c r="L424" t="s">
+        <v>15</v>
+      </c>
+      <c r="M424">
+        <v>6391.125</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A425">
+        <v>2026</v>
+      </c>
+      <c r="B425">
+        <v>5</v>
+      </c>
+      <c r="C425" t="s">
+        <v>61</v>
+      </c>
+      <c r="D425">
+        <v>433</v>
+      </c>
+      <c r="E425">
+        <v>2</v>
+      </c>
+      <c r="F425" t="s">
+        <v>14</v>
+      </c>
+      <c r="G425">
+        <v>8</v>
+      </c>
+      <c r="H425">
+        <v>23</v>
+      </c>
+      <c r="I425">
+        <v>1</v>
+      </c>
+      <c r="J425" t="s">
+        <v>15</v>
+      </c>
+      <c r="K425" t="s">
+        <v>15</v>
+      </c>
+      <c r="L425" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M425" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A426">
+        <v>2026</v>
+      </c>
+      <c r="B426">
+        <v>5</v>
+      </c>
+      <c r="C426" t="s">
+        <v>61</v>
+      </c>
+      <c r="D426">
+        <v>534</v>
+      </c>
+      <c r="E426">
+        <v>1</v>
+      </c>
+      <c r="F426" t="s">
+        <v>14</v>
+      </c>
+      <c r="G426">
+        <v>8</v>
+      </c>
+      <c r="H426">
+        <v>23</v>
+      </c>
+      <c r="I426">
+        <v>1</v>
+      </c>
+      <c r="J426" t="s">
+        <v>15</v>
+      </c>
+      <c r="K426" t="s">
+        <v>15</v>
+      </c>
+      <c r="L426" t="s">
+        <v>15</v>
+      </c>
+      <c r="M426">
+        <v>7261.6750000000002</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A427">
+        <v>2026</v>
+      </c>
+      <c r="B427">
+        <v>5</v>
+      </c>
+      <c r="C427" t="s">
+        <v>61</v>
+      </c>
+      <c r="D427">
+        <v>535</v>
+      </c>
+      <c r="E427">
+        <v>1</v>
+      </c>
+      <c r="F427" t="s">
+        <v>14</v>
+      </c>
+      <c r="G427">
+        <v>8</v>
+      </c>
+      <c r="H427">
+        <v>29</v>
+      </c>
+      <c r="I427">
+        <v>1</v>
+      </c>
+      <c r="J427" t="s">
+        <v>15</v>
+      </c>
+      <c r="K427" t="s">
+        <v>15</v>
+      </c>
+      <c r="L427" t="s">
+        <v>15</v>
+      </c>
+      <c r="M427">
+        <v>6781.2624999999998</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A428">
+        <v>2026</v>
+      </c>
+      <c r="B428">
+        <v>5</v>
+      </c>
+      <c r="C428" t="s">
+        <v>61</v>
+      </c>
+      <c r="D428">
+        <v>535</v>
+      </c>
+      <c r="E428">
+        <v>1</v>
+      </c>
+      <c r="F428" t="s">
+        <v>14</v>
+      </c>
+      <c r="H428" t="s">
+        <v>15</v>
+      </c>
+      <c r="I428" t="s">
+        <v>15</v>
+      </c>
+      <c r="J428">
+        <v>1</v>
+      </c>
+      <c r="K428" t="s">
+        <v>64</v>
+      </c>
+      <c r="L428" t="s">
+        <v>15</v>
+      </c>
+      <c r="M428">
+        <v>6781.2624999999998</v>
       </c>
     </row>
   </sheetData>
